--- a/public/work-report-default-template.xlsx
+++ b/public/work-report-default-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E0C72B-635A-4B15-BBEB-1C57D10ED683}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FA00A4B-8064-4BA4-B681-805A42B87ADA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,6 +790,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -800,17 +830,198 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -818,27 +1029,12 @@
     <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -848,225 +1044,29 @@
     <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1130,6 +1130,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1442,54 +1446,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A1" s="74"/>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="77" t="s">
+      <c r="Q1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="78"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
     </row>
     <row r="2" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="A2" s="36"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
-      <c r="V2" s="97"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
     </row>
     <row r="3" spans="1:22" ht="23.1" customHeight="1">
       <c r="A3" s="6"/>
@@ -1516,64 +1520,64 @@
       <c r="V3" s="7"/>
     </row>
     <row r="4" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="42"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="44"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="80" t="s">
+      <c r="I4" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="81"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="90"/>
-      <c r="O4" s="91" t="s">
+      <c r="J4" s="46"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="55"/>
+      <c r="O4" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="84"/>
-      <c r="T4" s="85"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="50"/>
       <c r="U4" s="7"/>
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="42"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="44"/>
       <c r="H5" s="12"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="95"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="88"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="60"/>
+      <c r="R5" s="51"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="53"/>
       <c r="U5" s="7"/>
       <c r="V5" s="16"/>
     </row>
     <row r="6" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="42"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="44"/>
       <c r="H6" s="12"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -1589,15 +1593,15 @@
       <c r="V6" s="15"/>
     </row>
     <row r="7" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="39"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="101"/>
       <c r="H7" s="12"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -1614,28 +1618,28 @@
       <c r="V7" s="15"/>
     </row>
     <row r="8" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="66"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="87"/>
       <c r="H8" s="7"/>
       <c r="U8" s="7"/>
     </row>
     <row r="9" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="66"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="87"/>
       <c r="H9" s="7"/>
       <c r="O9" s="7"/>
       <c r="U9" s="7"/>
@@ -1666,134 +1670,134 @@
       <c r="V10" s="7"/>
     </row>
     <row r="11" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="67"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="53" t="s">
+      <c r="B11" s="88"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="54"/>
-      <c r="F11" s="53" t="s">
+      <c r="E11" s="75"/>
+      <c r="F11" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="54"/>
-      <c r="H11" s="53" t="s">
+      <c r="G11" s="75"/>
+      <c r="H11" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="54"/>
-      <c r="J11" s="57" t="s">
+      <c r="I11" s="75"/>
+      <c r="J11" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="58"/>
-      <c r="L11" s="57" t="s">
+      <c r="K11" s="79"/>
+      <c r="L11" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61"/>
-      <c r="P11" s="61"/>
-      <c r="Q11" s="61"/>
-      <c r="R11" s="61"/>
-      <c r="S11" s="61"/>
-      <c r="T11" s="61"/>
-      <c r="U11" s="61"/>
-      <c r="V11" s="58"/>
+      <c r="M11" s="82"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="79"/>
     </row>
     <row r="12" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A12" s="69"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="59"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="62"/>
-      <c r="O12" s="62"/>
-      <c r="P12" s="62"/>
-      <c r="Q12" s="62"/>
-      <c r="R12" s="62"/>
-      <c r="S12" s="62"/>
-      <c r="T12" s="62"/>
-      <c r="U12" s="62"/>
-      <c r="V12" s="60"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="80"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="83"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="83"/>
+      <c r="Q12" s="83"/>
+      <c r="R12" s="83"/>
+      <c r="S12" s="83"/>
+      <c r="T12" s="83"/>
+      <c r="U12" s="83"/>
+      <c r="V12" s="81"/>
     </row>
     <row r="13" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="28">
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="95">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="28">
+      <c r="E13" s="96"/>
+      <c r="F13" s="95">
         <v>0.79166666666666663</v>
       </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="32">
+      <c r="G13" s="96"/>
+      <c r="H13" s="97">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I13" s="33"/>
-      <c r="J13" s="28">
+      <c r="I13" s="98"/>
+      <c r="J13" s="95">
         <v>0.33333333333333331</v>
       </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="47" t="s">
+      <c r="K13" s="96"/>
+      <c r="L13" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48"/>
-      <c r="V13" s="49"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="69"/>
+      <c r="O13" s="69"/>
+      <c r="P13" s="69"/>
+      <c r="Q13" s="69"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="69"/>
+      <c r="T13" s="69"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="70"/>
     </row>
     <row r="14" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A14" s="30"/>
-      <c r="B14" s="31"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="24"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="19"/>
       <c r="G14" s="20"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="45" t="str">
+      <c r="H14" s="64"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66" t="str">
         <f t="shared" ref="J14" si="0">IF(D14="","",(ABS(F14-D14))-H14)</f>
         <v/>
       </c>
-      <c r="K14" s="46"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="51"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="51"/>
-      <c r="S14" s="51"/>
-      <c r="T14" s="51"/>
-      <c r="U14" s="51"/>
-      <c r="V14" s="52"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="73"/>
     </row>
     <row r="15" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A15" s="30"/>
-      <c r="B15" s="31"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="33"/>
       <c r="F15" s="19"/>
       <c r="G15" s="20"/>
       <c r="H15" s="19"/>
@@ -1802,7 +1806,7 @@
         <f t="shared" ref="J15:J44" si="1">IF(D15="","",(ABS(F15-D15))-H15)</f>
         <v/>
       </c>
-      <c r="K15" s="22"/>
+      <c r="K15" s="31"/>
       <c r="L15" s="25"/>
       <c r="M15" s="26"/>
       <c r="N15" s="26"/>
@@ -1816,11 +1820,11 @@
       <c r="V15" s="27"/>
     </row>
     <row r="16" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="19"/>
       <c r="G16" s="20"/>
       <c r="H16" s="19"/>
@@ -1829,7 +1833,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K16" s="22"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="25"/>
       <c r="M16" s="26"/>
       <c r="N16" s="26"/>
@@ -1843,20 +1847,20 @@
       <c r="V16" s="27"/>
     </row>
     <row r="17" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A17" s="30"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="24"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="33"/>
       <c r="H17" s="19"/>
       <c r="I17" s="20"/>
       <c r="J17" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="22"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="25"/>
       <c r="M17" s="26"/>
       <c r="N17" s="26"/>
@@ -1870,20 +1874,20 @@
       <c r="V17" s="27"/>
     </row>
     <row r="18" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A18" s="30"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="19"/>
       <c r="I18" s="20"/>
       <c r="J18" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="22"/>
+      <c r="K18" s="31"/>
       <c r="L18" s="25"/>
       <c r="M18" s="26"/>
       <c r="N18" s="26"/>
@@ -1897,11 +1901,11 @@
       <c r="V18" s="27"/>
     </row>
     <row r="19" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A19" s="30"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="24"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
       <c r="H19" s="19"/>
@@ -1910,7 +1914,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="22"/>
+      <c r="K19" s="31"/>
       <c r="L19" s="25"/>
       <c r="M19" s="26"/>
       <c r="N19" s="26"/>
@@ -1924,11 +1928,11 @@
       <c r="V19" s="27"/>
     </row>
     <row r="20" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="24"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="19"/>
@@ -1937,7 +1941,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="22"/>
+      <c r="K20" s="31"/>
       <c r="L20" s="25"/>
       <c r="M20" s="26"/>
       <c r="N20" s="26"/>
@@ -1951,11 +1955,11 @@
       <c r="V20" s="27"/>
     </row>
     <row r="21" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
       <c r="F21" s="19"/>
       <c r="G21" s="20"/>
       <c r="H21" s="19"/>
@@ -1964,7 +1968,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="22"/>
+      <c r="K21" s="31"/>
       <c r="L21" s="25"/>
       <c r="M21" s="26"/>
       <c r="N21" s="26"/>
@@ -1978,11 +1982,11 @@
       <c r="V21" s="27"/>
     </row>
     <row r="22" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A22" s="30"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="24"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
       <c r="F22" s="19"/>
       <c r="G22" s="20"/>
       <c r="H22" s="19"/>
@@ -1991,7 +1995,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="22"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="25"/>
       <c r="M22" s="26"/>
       <c r="N22" s="26"/>
@@ -2005,11 +2009,11 @@
       <c r="V22" s="27"/>
     </row>
     <row r="23" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A23" s="30"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
       <c r="F23" s="19"/>
       <c r="G23" s="20"/>
       <c r="H23" s="19"/>
@@ -2018,7 +2022,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="22"/>
+      <c r="K23" s="31"/>
       <c r="L23" s="25"/>
       <c r="M23" s="26"/>
       <c r="N23" s="26"/>
@@ -2032,8 +2036,8 @@
       <c r="V23" s="27"/>
     </row>
     <row r="24" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A24" s="30"/>
-      <c r="B24" s="31"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="8"/>
       <c r="D24" s="19"/>
       <c r="E24" s="20"/>
@@ -2045,7 +2049,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="22"/>
+      <c r="K24" s="31"/>
       <c r="L24" s="25"/>
       <c r="M24" s="26"/>
       <c r="N24" s="26"/>
@@ -2059,8 +2063,8 @@
       <c r="V24" s="27"/>
     </row>
     <row r="25" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A25" s="30"/>
-      <c r="B25" s="31"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="24"/>
       <c r="C25" s="8"/>
       <c r="D25" s="19"/>
       <c r="E25" s="20"/>
@@ -2072,7 +2076,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="22"/>
+      <c r="K25" s="31"/>
       <c r="L25" s="25"/>
       <c r="M25" s="26"/>
       <c r="N25" s="26"/>
@@ -2086,11 +2090,11 @@
       <c r="V25" s="27"/>
     </row>
     <row r="26" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A26" s="30"/>
-      <c r="B26" s="31"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="24"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="24"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="19"/>
       <c r="G26" s="20"/>
       <c r="H26" s="19"/>
@@ -2099,7 +2103,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="22"/>
+      <c r="K26" s="31"/>
       <c r="L26" s="25"/>
       <c r="M26" s="26"/>
       <c r="N26" s="26"/>
@@ -2113,11 +2117,11 @@
       <c r="V26" s="27"/>
     </row>
     <row r="27" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A27" s="30"/>
-      <c r="B27" s="31"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="24"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="24"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="33"/>
       <c r="F27" s="19"/>
       <c r="G27" s="20"/>
       <c r="H27" s="19"/>
@@ -2126,7 +2130,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="22"/>
+      <c r="K27" s="31"/>
       <c r="L27" s="25"/>
       <c r="M27" s="26"/>
       <c r="N27" s="26"/>
@@ -2140,11 +2144,11 @@
       <c r="V27" s="27"/>
     </row>
     <row r="28" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A28" s="30"/>
-      <c r="B28" s="31"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="24"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="24"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33"/>
       <c r="F28" s="19"/>
       <c r="G28" s="20"/>
       <c r="H28" s="19"/>
@@ -2153,7 +2157,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="22"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="25"/>
       <c r="M28" s="26"/>
       <c r="N28" s="26"/>
@@ -2167,11 +2171,11 @@
       <c r="V28" s="27"/>
     </row>
     <row r="29" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A29" s="30"/>
-      <c r="B29" s="31"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="24"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="33"/>
       <c r="F29" s="19"/>
       <c r="G29" s="20"/>
       <c r="H29" s="19"/>
@@ -2180,7 +2184,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="22"/>
+      <c r="K29" s="31"/>
       <c r="L29" s="25"/>
       <c r="M29" s="26"/>
       <c r="N29" s="26"/>
@@ -2194,11 +2198,11 @@
       <c r="V29" s="27"/>
     </row>
     <row r="30" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A30" s="30"/>
-      <c r="B30" s="31"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="24"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="24"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="33"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="19"/>
@@ -2207,7 +2211,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="22"/>
+      <c r="K30" s="31"/>
       <c r="L30" s="25"/>
       <c r="M30" s="26"/>
       <c r="N30" s="26"/>
@@ -2221,8 +2225,8 @@
       <c r="V30" s="27"/>
     </row>
     <row r="31" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A31" s="30"/>
-      <c r="B31" s="31"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="24"/>
       <c r="C31" s="8"/>
       <c r="D31" s="19"/>
       <c r="E31" s="20"/>
@@ -2234,7 +2238,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="22"/>
+      <c r="K31" s="31"/>
       <c r="L31" s="25"/>
       <c r="M31" s="26"/>
       <c r="N31" s="26"/>
@@ -2248,8 +2252,8 @@
       <c r="V31" s="27"/>
     </row>
     <row r="32" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A32" s="30"/>
-      <c r="B32" s="31"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="24"/>
       <c r="C32" s="8"/>
       <c r="D32" s="19"/>
       <c r="E32" s="20"/>
@@ -2261,7 +2265,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="22"/>
+      <c r="K32" s="31"/>
       <c r="L32" s="25"/>
       <c r="M32" s="26"/>
       <c r="N32" s="26"/>
@@ -2275,8 +2279,8 @@
       <c r="V32" s="27"/>
     </row>
     <row r="33" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A33" s="30"/>
-      <c r="B33" s="31"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="24"/>
       <c r="C33" s="8"/>
       <c r="D33" s="19"/>
       <c r="E33" s="20"/>
@@ -2288,7 +2292,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="22"/>
+      <c r="K33" s="31"/>
       <c r="L33" s="25"/>
       <c r="M33" s="26"/>
       <c r="N33" s="26"/>
@@ -2302,11 +2306,11 @@
       <c r="V33" s="27"/>
     </row>
     <row r="34" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A34" s="30"/>
-      <c r="B34" s="31"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="24"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="24"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="33"/>
       <c r="F34" s="19"/>
       <c r="G34" s="20"/>
       <c r="H34" s="19"/>
@@ -2315,7 +2319,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="22"/>
+      <c r="K34" s="31"/>
       <c r="L34" s="25"/>
       <c r="M34" s="26"/>
       <c r="N34" s="26"/>
@@ -2329,11 +2333,11 @@
       <c r="V34" s="27"/>
     </row>
     <row r="35" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A35" s="30"/>
-      <c r="B35" s="31"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="24"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="24"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="33"/>
       <c r="F35" s="19"/>
       <c r="G35" s="20"/>
       <c r="H35" s="19"/>
@@ -2342,7 +2346,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="22"/>
+      <c r="K35" s="31"/>
       <c r="L35" s="25"/>
       <c r="M35" s="26"/>
       <c r="N35" s="26"/>
@@ -2356,11 +2360,11 @@
       <c r="V35" s="27"/>
     </row>
     <row r="36" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A36" s="30"/>
-      <c r="B36" s="31"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="24"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="24"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="33"/>
       <c r="F36" s="19"/>
       <c r="G36" s="20"/>
       <c r="H36" s="19"/>
@@ -2369,7 +2373,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="22"/>
+      <c r="K36" s="31"/>
       <c r="L36" s="25"/>
       <c r="M36" s="26"/>
       <c r="N36" s="26"/>
@@ -2383,11 +2387,11 @@
       <c r="V36" s="27"/>
     </row>
     <row r="37" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A37" s="30"/>
-      <c r="B37" s="31"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="24"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="24"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="33"/>
       <c r="F37" s="19"/>
       <c r="G37" s="20"/>
       <c r="H37" s="19"/>
@@ -2396,7 +2400,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="22"/>
+      <c r="K37" s="31"/>
       <c r="L37" s="25"/>
       <c r="M37" s="26"/>
       <c r="N37" s="26"/>
@@ -2410,8 +2414,8 @@
       <c r="V37" s="27"/>
     </row>
     <row r="38" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A38" s="30"/>
-      <c r="B38" s="31"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="24"/>
       <c r="C38" s="8"/>
       <c r="D38" s="19"/>
       <c r="E38" s="20"/>
@@ -2423,7 +2427,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="22"/>
+      <c r="K38" s="31"/>
       <c r="L38" s="25"/>
       <c r="M38" s="26"/>
       <c r="N38" s="26"/>
@@ -2437,8 +2441,8 @@
       <c r="V38" s="27"/>
     </row>
     <row r="39" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A39" s="30"/>
-      <c r="B39" s="31"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="24"/>
       <c r="C39" s="8"/>
       <c r="D39" s="19"/>
       <c r="E39" s="20"/>
@@ -2450,7 +2454,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="107"/>
+      <c r="K39" s="22"/>
       <c r="L39" s="25"/>
       <c r="M39" s="26"/>
       <c r="N39" s="26"/>
@@ -2464,8 +2468,8 @@
       <c r="V39" s="27"/>
     </row>
     <row r="40" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A40" s="30"/>
-      <c r="B40" s="31"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="24"/>
       <c r="C40" s="8"/>
       <c r="D40" s="19"/>
       <c r="E40" s="20"/>
@@ -2477,7 +2481,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="107"/>
+      <c r="K40" s="22"/>
       <c r="L40" s="25"/>
       <c r="M40" s="26"/>
       <c r="N40" s="26"/>
@@ -2491,8 +2495,8 @@
       <c r="V40" s="27"/>
     </row>
     <row r="41" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A41" s="30"/>
-      <c r="B41" s="31"/>
+      <c r="A41" s="23"/>
+      <c r="B41" s="24"/>
       <c r="C41" s="8"/>
       <c r="D41" s="19"/>
       <c r="E41" s="20"/>
@@ -2504,7 +2508,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="107"/>
+      <c r="K41" s="22"/>
       <c r="L41" s="25"/>
       <c r="M41" s="26"/>
       <c r="N41" s="26"/>
@@ -2518,11 +2522,11 @@
       <c r="V41" s="27"/>
     </row>
     <row r="42" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
+      <c r="A42" s="23"/>
+      <c r="B42" s="24"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="24"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="33"/>
       <c r="F42" s="19"/>
       <c r="G42" s="20"/>
       <c r="H42" s="19"/>
@@ -2531,7 +2535,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="22"/>
+      <c r="K42" s="31"/>
       <c r="L42" s="25"/>
       <c r="M42" s="26"/>
       <c r="N42" s="26"/>
@@ -2545,11 +2549,11 @@
       <c r="V42" s="27"/>
     </row>
     <row r="43" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A43" s="30"/>
-      <c r="B43" s="31"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="24"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="24"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="33"/>
       <c r="F43" s="19"/>
       <c r="G43" s="20"/>
       <c r="H43" s="19"/>
@@ -2558,7 +2562,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="22"/>
+      <c r="K43" s="31"/>
       <c r="L43" s="25"/>
       <c r="M43" s="26"/>
       <c r="N43" s="26"/>
@@ -2572,8 +2576,8 @@
       <c r="V43" s="27"/>
     </row>
     <row r="44" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="24"/>
       <c r="C44" s="8"/>
       <c r="D44" s="19"/>
       <c r="E44" s="20"/>
@@ -2585,7 +2589,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K44" s="22"/>
+      <c r="K44" s="31"/>
       <c r="L44" s="25"/>
       <c r="M44" s="26"/>
       <c r="N44" s="26"/>
@@ -2623,122 +2627,285 @@
       <c r="V45" s="9"/>
     </row>
     <row r="46" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A46" s="104" t="s">
+      <c r="A46" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="105"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="105"/>
-      <c r="I46" s="105"/>
-      <c r="J46" s="105"/>
-      <c r="K46" s="105"/>
-      <c r="L46" s="105"/>
-      <c r="M46" s="105"/>
-      <c r="N46" s="105"/>
-      <c r="O46" s="105"/>
-      <c r="P46" s="105"/>
-      <c r="Q46" s="105"/>
-      <c r="R46" s="105"/>
-      <c r="S46" s="105"/>
-      <c r="T46" s="105"/>
-      <c r="U46" s="105"/>
-      <c r="V46" s="106"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="30"/>
     </row>
     <row r="47" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A47" s="98"/>
-      <c r="B47" s="99"/>
-      <c r="C47" s="99"/>
-      <c r="D47" s="99"/>
-      <c r="E47" s="99"/>
-      <c r="F47" s="99"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="99"/>
-      <c r="I47" s="99"/>
-      <c r="J47" s="99"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="99"/>
-      <c r="N47" s="99"/>
-      <c r="O47" s="99"/>
-      <c r="P47" s="99"/>
-      <c r="Q47" s="99"/>
-      <c r="R47" s="99"/>
-      <c r="S47" s="99"/>
-      <c r="T47" s="99"/>
-      <c r="U47" s="99"/>
-      <c r="V47" s="100"/>
+      <c r="A47" s="102"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="103"/>
+      <c r="D47" s="103"/>
+      <c r="E47" s="103"/>
+      <c r="F47" s="103"/>
+      <c r="G47" s="103"/>
+      <c r="H47" s="103"/>
+      <c r="I47" s="103"/>
+      <c r="J47" s="103"/>
+      <c r="K47" s="103"/>
+      <c r="L47" s="103"/>
+      <c r="M47" s="103"/>
+      <c r="N47" s="103"/>
+      <c r="O47" s="103"/>
+      <c r="P47" s="103"/>
+      <c r="Q47" s="103"/>
+      <c r="R47" s="103"/>
+      <c r="S47" s="103"/>
+      <c r="T47" s="103"/>
+      <c r="U47" s="103"/>
+      <c r="V47" s="104"/>
     </row>
     <row r="48" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A48" s="98"/>
-      <c r="B48" s="99"/>
-      <c r="C48" s="99"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
-      <c r="H48" s="99"/>
-      <c r="I48" s="99"/>
-      <c r="J48" s="99"/>
-      <c r="K48" s="99"/>
-      <c r="L48" s="99"/>
-      <c r="M48" s="99"/>
-      <c r="N48" s="99"/>
-      <c r="O48" s="99"/>
-      <c r="P48" s="99"/>
-      <c r="Q48" s="99"/>
-      <c r="R48" s="99"/>
-      <c r="S48" s="99"/>
-      <c r="T48" s="99"/>
-      <c r="U48" s="99"/>
-      <c r="V48" s="100"/>
+      <c r="A48" s="102"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="103"/>
+      <c r="D48" s="103"/>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="103"/>
+      <c r="K48" s="103"/>
+      <c r="L48" s="103"/>
+      <c r="M48" s="103"/>
+      <c r="N48" s="103"/>
+      <c r="O48" s="103"/>
+      <c r="P48" s="103"/>
+      <c r="Q48" s="103"/>
+      <c r="R48" s="103"/>
+      <c r="S48" s="103"/>
+      <c r="T48" s="103"/>
+      <c r="U48" s="103"/>
+      <c r="V48" s="104"/>
     </row>
     <row r="49" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A49" s="101"/>
-      <c r="B49" s="102"/>
-      <c r="C49" s="102"/>
-      <c r="D49" s="102"/>
-      <c r="E49" s="102"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="102"/>
-      <c r="H49" s="102"/>
-      <c r="I49" s="102"/>
-      <c r="J49" s="102"/>
-      <c r="K49" s="102"/>
-      <c r="L49" s="102"/>
-      <c r="M49" s="102"/>
-      <c r="N49" s="102"/>
-      <c r="O49" s="102"/>
-      <c r="P49" s="102"/>
-      <c r="Q49" s="102"/>
-      <c r="R49" s="102"/>
-      <c r="S49" s="102"/>
-      <c r="T49" s="102"/>
-      <c r="U49" s="102"/>
-      <c r="V49" s="103"/>
+      <c r="A49" s="105"/>
+      <c r="B49" s="106"/>
+      <c r="C49" s="106"/>
+      <c r="D49" s="106"/>
+      <c r="E49" s="106"/>
+      <c r="F49" s="106"/>
+      <c r="G49" s="106"/>
+      <c r="H49" s="106"/>
+      <c r="I49" s="106"/>
+      <c r="J49" s="106"/>
+      <c r="K49" s="106"/>
+      <c r="L49" s="106"/>
+      <c r="M49" s="106"/>
+      <c r="N49" s="106"/>
+      <c r="O49" s="106"/>
+      <c r="P49" s="106"/>
+      <c r="Q49" s="106"/>
+      <c r="R49" s="106"/>
+      <c r="S49" s="106"/>
+      <c r="T49" s="106"/>
+      <c r="U49" s="106"/>
+      <c r="V49" s="107"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="219">
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="L39:V39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L20:V20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="L19:V19"/>
+    <mergeCell ref="L18:V18"/>
+    <mergeCell ref="L17:V17"/>
+    <mergeCell ref="L16:V16"/>
+    <mergeCell ref="L15:V15"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L13:V13"/>
+    <mergeCell ref="L14:V14"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="J11:K12"/>
+    <mergeCell ref="L11:V12"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="Q1:R2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="R4:T5"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="O4:Q5"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="S1:V2"/>
+    <mergeCell ref="L35:V35"/>
+    <mergeCell ref="L36:V36"/>
+    <mergeCell ref="L37:V37"/>
+    <mergeCell ref="L38:V38"/>
+    <mergeCell ref="L21:V21"/>
+    <mergeCell ref="L22:V22"/>
+    <mergeCell ref="L23:V23"/>
+    <mergeCell ref="L24:V24"/>
+    <mergeCell ref="L25:V25"/>
+    <mergeCell ref="L26:V26"/>
+    <mergeCell ref="L27:V27"/>
+    <mergeCell ref="L28:V28"/>
+    <mergeCell ref="L29:V29"/>
+    <mergeCell ref="L32:V32"/>
+    <mergeCell ref="L31:V31"/>
+    <mergeCell ref="L30:V30"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="A47:V49"/>
     <mergeCell ref="A46:V46"/>
     <mergeCell ref="L44:V44"/>
@@ -2763,185 +2930,22 @@
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="H43:I43"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="L35:V35"/>
-    <mergeCell ref="L36:V36"/>
-    <mergeCell ref="L37:V37"/>
-    <mergeCell ref="L38:V38"/>
-    <mergeCell ref="L21:V21"/>
-    <mergeCell ref="L22:V22"/>
-    <mergeCell ref="L23:V23"/>
-    <mergeCell ref="L24:V24"/>
-    <mergeCell ref="L25:V25"/>
-    <mergeCell ref="L26:V26"/>
-    <mergeCell ref="L27:V27"/>
-    <mergeCell ref="L28:V28"/>
-    <mergeCell ref="L29:V29"/>
-    <mergeCell ref="L32:V32"/>
-    <mergeCell ref="L31:V31"/>
-    <mergeCell ref="L30:V30"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="Q1:R2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="R4:T5"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="O4:Q5"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="S1:V2"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L13:V13"/>
-    <mergeCell ref="L14:V14"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="J11:K12"/>
-    <mergeCell ref="L11:V12"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L20:V20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="L19:V19"/>
-    <mergeCell ref="L18:V18"/>
-    <mergeCell ref="L17:V17"/>
-    <mergeCell ref="L16:V16"/>
-    <mergeCell ref="L15:V15"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="L39:V39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J39:K39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:J2 E8:G9">

--- a/public/work-report-default-template.xlsx
+++ b/public/work-report-default-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FA00A4B-8064-4BA4-B681-805A42B87ADA}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE6AEA65-7C64-45A6-906A-03449807D26B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="作業報告書" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_１ヶ月あたりの作業単位">作業報告書!$E$9</definedName>
-    <definedName name="_１日あたりの作業単位">作業報告書!$E$8</definedName>
+    <definedName name="_1ヶ月あたりの作業単位">作業報告書!$E$9</definedName>
+    <definedName name="_1日あたりの作業単位">作業報告書!$E$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">作業報告書!$A$1:$V$49</definedName>
     <definedName name="タイトル">作業報告書!$A$1</definedName>
     <definedName name="稼働時間">作業報告書!$J$14:$K$44</definedName>
@@ -790,7 +790,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -798,6 +798,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
@@ -810,6 +836,226 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -820,253 +1066,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1446,54 +1446,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="A1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="38"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="61"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
     </row>
     <row r="2" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
     </row>
     <row r="3" spans="1:22" ht="23.1" customHeight="1">
       <c r="A3" s="6"/>
@@ -1520,64 +1520,64 @@
       <c r="V3" s="7"/>
     </row>
     <row r="4" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="44"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="45" t="s">
+      <c r="I4" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="46"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="55"/>
-      <c r="O4" s="56" t="s">
+      <c r="J4" s="81"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="90"/>
+      <c r="O4" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="50"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="84"/>
+      <c r="T4" s="85"/>
       <c r="U4" s="7"/>
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="44"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38"/>
       <c r="H5" s="12"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="53"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="86"/>
+      <c r="S5" s="87"/>
+      <c r="T5" s="88"/>
       <c r="U5" s="7"/>
       <c r="V5" s="16"/>
     </row>
     <row r="6" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
       <c r="H6" s="12"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -1593,15 +1593,15 @@
       <c r="V6" s="15"/>
     </row>
     <row r="7" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="101"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="32"/>
       <c r="H7" s="12"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -1618,28 +1618,28 @@
       <c r="V7" s="15"/>
     </row>
     <row r="8" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="87"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="62"/>
       <c r="H8" s="7"/>
       <c r="U8" s="7"/>
     </row>
     <row r="9" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="87"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="62"/>
       <c r="H9" s="7"/>
       <c r="O9" s="7"/>
       <c r="U9" s="7"/>
@@ -1670,134 +1670,134 @@
       <c r="V10" s="7"/>
     </row>
     <row r="11" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="88"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="74" t="s">
+      <c r="B11" s="63"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="75"/>
-      <c r="F11" s="74" t="s">
+      <c r="E11" s="50"/>
+      <c r="F11" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="75"/>
-      <c r="H11" s="74" t="s">
+      <c r="G11" s="50"/>
+      <c r="H11" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="75"/>
-      <c r="J11" s="78" t="s">
+      <c r="I11" s="50"/>
+      <c r="J11" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="79"/>
-      <c r="L11" s="78" t="s">
+      <c r="K11" s="54"/>
+      <c r="L11" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="82"/>
-      <c r="N11" s="82"/>
-      <c r="O11" s="82"/>
-      <c r="P11" s="82"/>
-      <c r="Q11" s="82"/>
-      <c r="R11" s="82"/>
-      <c r="S11" s="82"/>
-      <c r="T11" s="82"/>
-      <c r="U11" s="82"/>
-      <c r="V11" s="79"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="57"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="57"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="57"/>
+      <c r="V11" s="54"/>
     </row>
     <row r="12" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A12" s="90"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="92"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="80"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="80"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="83"/>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="83"/>
-      <c r="R12" s="83"/>
-      <c r="S12" s="83"/>
-      <c r="T12" s="83"/>
-      <c r="U12" s="83"/>
-      <c r="V12" s="81"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="58"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="58"/>
+      <c r="S12" s="58"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="58"/>
+      <c r="V12" s="56"/>
     </row>
     <row r="13" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="95">
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E13" s="96"/>
-      <c r="F13" s="95">
+      <c r="E13" s="71"/>
+      <c r="F13" s="70">
         <v>0.79166666666666663</v>
       </c>
-      <c r="G13" s="96"/>
-      <c r="H13" s="97">
+      <c r="G13" s="71"/>
+      <c r="H13" s="72">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I13" s="98"/>
-      <c r="J13" s="95">
+      <c r="I13" s="73"/>
+      <c r="J13" s="70">
         <v>0.33333333333333331</v>
       </c>
-      <c r="K13" s="96"/>
-      <c r="L13" s="68" t="s">
+      <c r="K13" s="71"/>
+      <c r="L13" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="69"/>
-      <c r="P13" s="69"/>
-      <c r="Q13" s="69"/>
-      <c r="R13" s="69"/>
-      <c r="S13" s="69"/>
-      <c r="T13" s="69"/>
-      <c r="U13" s="69"/>
-      <c r="V13" s="70"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="45"/>
     </row>
     <row r="14" spans="1:22" ht="23.1" customHeight="1">
       <c r="A14" s="23"/>
       <c r="B14" s="24"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="33"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="26"/>
       <c r="F14" s="19"/>
       <c r="G14" s="20"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="66" t="str">
+      <c r="H14" s="39"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="41" t="str">
         <f t="shared" ref="J14" si="0">IF(D14="","",(ABS(F14-D14))-H14)</f>
         <v/>
       </c>
-      <c r="K14" s="67"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="72"/>
-      <c r="T14" s="72"/>
-      <c r="U14" s="72"/>
-      <c r="V14" s="73"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="48"/>
     </row>
     <row r="15" spans="1:22" ht="23.1" customHeight="1">
       <c r="A15" s="23"/>
       <c r="B15" s="24"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="33"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="19"/>
       <c r="G15" s="20"/>
       <c r="H15" s="19"/>
@@ -1806,25 +1806,25 @@
         <f t="shared" ref="J15:J44" si="1">IF(D15="","",(ABS(F15-D15))-H15)</f>
         <v/>
       </c>
-      <c r="K15" s="31"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
-      <c r="V15" s="27"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="34"/>
+      <c r="V15" s="35"/>
     </row>
     <row r="16" spans="1:22" ht="23.1" customHeight="1">
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="26"/>
       <c r="F16" s="19"/>
       <c r="G16" s="20"/>
       <c r="H16" s="19"/>
@@ -1833,79 +1833,79 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K16" s="31"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="26"/>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="27"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="35"/>
     </row>
     <row r="17" spans="1:22" ht="23.1" customHeight="1">
       <c r="A17" s="23"/>
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="33"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="19"/>
       <c r="I17" s="20"/>
       <c r="J17" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="31"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="26"/>
-      <c r="S17" s="26"/>
-      <c r="T17" s="26"/>
-      <c r="U17" s="26"/>
-      <c r="V17" s="27"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="35"/>
     </row>
     <row r="18" spans="1:22" ht="23.1" customHeight="1">
       <c r="A18" s="23"/>
       <c r="B18" s="24"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="33"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="26"/>
       <c r="H18" s="19"/>
       <c r="I18" s="20"/>
       <c r="J18" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="31"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-      <c r="V18" s="27"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="34"/>
+      <c r="V18" s="35"/>
     </row>
     <row r="19" spans="1:22" ht="23.1" customHeight="1">
       <c r="A19" s="23"/>
       <c r="B19" s="24"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
       <c r="H19" s="19"/>
@@ -1914,25 +1914,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="31"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-      <c r="V19" s="27"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="34"/>
+      <c r="V19" s="35"/>
     </row>
     <row r="20" spans="1:22" ht="23.1" customHeight="1">
       <c r="A20" s="23"/>
       <c r="B20" s="24"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="19"/>
@@ -1941,25 +1941,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="31"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-      <c r="V20" s="27"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="35"/>
     </row>
     <row r="21" spans="1:22" ht="23.1" customHeight="1">
       <c r="A21" s="23"/>
       <c r="B21" s="24"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="19"/>
       <c r="G21" s="20"/>
       <c r="H21" s="19"/>
@@ -1968,25 +1968,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="31"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="27"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="34"/>
+      <c r="V21" s="35"/>
     </row>
     <row r="22" spans="1:22" ht="23.1" customHeight="1">
       <c r="A22" s="23"/>
       <c r="B22" s="24"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
       <c r="F22" s="19"/>
       <c r="G22" s="20"/>
       <c r="H22" s="19"/>
@@ -1995,25 +1995,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="31"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-      <c r="V22" s="27"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="35"/>
     </row>
     <row r="23" spans="1:22" ht="23.1" customHeight="1">
       <c r="A23" s="23"/>
       <c r="B23" s="24"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="26"/>
       <c r="F23" s="19"/>
       <c r="G23" s="20"/>
       <c r="H23" s="19"/>
@@ -2022,18 +2022,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="31"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="27"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="35"/>
     </row>
     <row r="24" spans="1:22" ht="23.1" customHeight="1">
       <c r="A24" s="23"/>
@@ -2049,18 +2049,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="31"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="27"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34"/>
+      <c r="S24" s="34"/>
+      <c r="T24" s="34"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="35"/>
     </row>
     <row r="25" spans="1:22" ht="23.1" customHeight="1">
       <c r="A25" s="23"/>
@@ -2076,25 +2076,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="31"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="26"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
-      <c r="V25" s="27"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="34"/>
+      <c r="S25" s="34"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="34"/>
+      <c r="V25" s="35"/>
     </row>
     <row r="26" spans="1:22" ht="23.1" customHeight="1">
       <c r="A26" s="23"/>
       <c r="B26" s="24"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="26"/>
       <c r="F26" s="19"/>
       <c r="G26" s="20"/>
       <c r="H26" s="19"/>
@@ -2103,25 +2103,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="31"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="27"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
+      <c r="S26" s="34"/>
+      <c r="T26" s="34"/>
+      <c r="U26" s="34"/>
+      <c r="V26" s="35"/>
     </row>
     <row r="27" spans="1:22" ht="23.1" customHeight="1">
       <c r="A27" s="23"/>
       <c r="B27" s="24"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="33"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="19"/>
       <c r="G27" s="20"/>
       <c r="H27" s="19"/>
@@ -2130,25 +2130,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="31"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="27"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="34"/>
+      <c r="S27" s="34"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="34"/>
+      <c r="V27" s="35"/>
     </row>
     <row r="28" spans="1:22" ht="23.1" customHeight="1">
       <c r="A28" s="23"/>
       <c r="B28" s="24"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
       <c r="F28" s="19"/>
       <c r="G28" s="20"/>
       <c r="H28" s="19"/>
@@ -2157,25 +2157,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="31"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="27"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="34"/>
+      <c r="V28" s="35"/>
     </row>
     <row r="29" spans="1:22" ht="23.1" customHeight="1">
       <c r="A29" s="23"/>
       <c r="B29" s="24"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="33"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="19"/>
       <c r="G29" s="20"/>
       <c r="H29" s="19"/>
@@ -2184,25 +2184,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="31"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="27"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="U29" s="34"/>
+      <c r="V29" s="35"/>
     </row>
     <row r="30" spans="1:22" ht="23.1" customHeight="1">
       <c r="A30" s="23"/>
       <c r="B30" s="24"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="33"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="26"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="19"/>
@@ -2211,18 +2211,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="31"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="27"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="35"/>
     </row>
     <row r="31" spans="1:22" ht="23.1" customHeight="1">
       <c r="A31" s="23"/>
@@ -2238,18 +2238,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="31"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="27"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="35"/>
     </row>
     <row r="32" spans="1:22" ht="23.1" customHeight="1">
       <c r="A32" s="23"/>
@@ -2265,18 +2265,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="31"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="27"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="V32" s="35"/>
     </row>
     <row r="33" spans="1:22" ht="23.1" customHeight="1">
       <c r="A33" s="23"/>
@@ -2292,25 +2292,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="31"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="27"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="34"/>
+      <c r="S33" s="34"/>
+      <c r="T33" s="34"/>
+      <c r="U33" s="34"/>
+      <c r="V33" s="35"/>
     </row>
     <row r="34" spans="1:22" ht="23.1" customHeight="1">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="33"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
       <c r="F34" s="19"/>
       <c r="G34" s="20"/>
       <c r="H34" s="19"/>
@@ -2319,25 +2319,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="31"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="27"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
+      <c r="P34" s="34"/>
+      <c r="Q34" s="34"/>
+      <c r="R34" s="34"/>
+      <c r="S34" s="34"/>
+      <c r="T34" s="34"/>
+      <c r="U34" s="34"/>
+      <c r="V34" s="35"/>
     </row>
     <row r="35" spans="1:22" ht="23.1" customHeight="1">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="33"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="26"/>
       <c r="F35" s="19"/>
       <c r="G35" s="20"/>
       <c r="H35" s="19"/>
@@ -2346,25 +2346,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="31"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="26"/>
-      <c r="V35" s="27"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="34"/>
+      <c r="S35" s="34"/>
+      <c r="T35" s="34"/>
+      <c r="U35" s="34"/>
+      <c r="V35" s="35"/>
     </row>
     <row r="36" spans="1:22" ht="23.1" customHeight="1">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="33"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="26"/>
       <c r="F36" s="19"/>
       <c r="G36" s="20"/>
       <c r="H36" s="19"/>
@@ -2373,25 +2373,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="31"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="26"/>
-      <c r="V36" s="27"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="34"/>
+      <c r="P36" s="34"/>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="34"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="34"/>
+      <c r="U36" s="34"/>
+      <c r="V36" s="35"/>
     </row>
     <row r="37" spans="1:22" ht="23.1" customHeight="1">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="33"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="26"/>
       <c r="F37" s="19"/>
       <c r="G37" s="20"/>
       <c r="H37" s="19"/>
@@ -2400,18 +2400,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="31"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="26"/>
-      <c r="V37" s="27"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="34"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="34"/>
+      <c r="R37" s="34"/>
+      <c r="S37" s="34"/>
+      <c r="T37" s="34"/>
+      <c r="U37" s="34"/>
+      <c r="V37" s="35"/>
     </row>
     <row r="38" spans="1:22" ht="23.1" customHeight="1">
       <c r="A38" s="23"/>
@@ -2427,18 +2427,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="31"/>
-      <c r="L38" s="25"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="27"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="34"/>
+      <c r="N38" s="34"/>
+      <c r="O38" s="34"/>
+      <c r="P38" s="34"/>
+      <c r="Q38" s="34"/>
+      <c r="R38" s="34"/>
+      <c r="S38" s="34"/>
+      <c r="T38" s="34"/>
+      <c r="U38" s="34"/>
+      <c r="V38" s="35"/>
     </row>
     <row r="39" spans="1:22" ht="23.1" customHeight="1">
       <c r="A39" s="23"/>
@@ -2454,18 +2454,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="22"/>
-      <c r="L39" s="25"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="26"/>
-      <c r="O39" s="26"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26"/>
-      <c r="S39" s="26"/>
-      <c r="T39" s="26"/>
-      <c r="U39" s="26"/>
-      <c r="V39" s="27"/>
+      <c r="K39" s="107"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="34"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="34"/>
+      <c r="P39" s="34"/>
+      <c r="Q39" s="34"/>
+      <c r="R39" s="34"/>
+      <c r="S39" s="34"/>
+      <c r="T39" s="34"/>
+      <c r="U39" s="34"/>
+      <c r="V39" s="35"/>
     </row>
     <row r="40" spans="1:22" ht="23.1" customHeight="1">
       <c r="A40" s="23"/>
@@ -2481,18 +2481,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="25"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="26"/>
-      <c r="Q40" s="26"/>
-      <c r="R40" s="26"/>
-      <c r="S40" s="26"/>
-      <c r="T40" s="26"/>
-      <c r="U40" s="26"/>
-      <c r="V40" s="27"/>
+      <c r="K40" s="107"/>
+      <c r="L40" s="33"/>
+      <c r="M40" s="34"/>
+      <c r="N40" s="34"/>
+      <c r="O40" s="34"/>
+      <c r="P40" s="34"/>
+      <c r="Q40" s="34"/>
+      <c r="R40" s="34"/>
+      <c r="S40" s="34"/>
+      <c r="T40" s="34"/>
+      <c r="U40" s="34"/>
+      <c r="V40" s="35"/>
     </row>
     <row r="41" spans="1:22" ht="23.1" customHeight="1">
       <c r="A41" s="23"/>
@@ -2508,25 +2508,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="22"/>
-      <c r="L41" s="25"/>
-      <c r="M41" s="26"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="26"/>
-      <c r="P41" s="26"/>
-      <c r="Q41" s="26"/>
-      <c r="R41" s="26"/>
-      <c r="S41" s="26"/>
-      <c r="T41" s="26"/>
-      <c r="U41" s="26"/>
-      <c r="V41" s="27"/>
+      <c r="K41" s="107"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="34"/>
+      <c r="N41" s="34"/>
+      <c r="O41" s="34"/>
+      <c r="P41" s="34"/>
+      <c r="Q41" s="34"/>
+      <c r="R41" s="34"/>
+      <c r="S41" s="34"/>
+      <c r="T41" s="34"/>
+      <c r="U41" s="34"/>
+      <c r="V41" s="35"/>
     </row>
     <row r="42" spans="1:22" ht="23.1" customHeight="1">
       <c r="A42" s="23"/>
       <c r="B42" s="24"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="33"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="26"/>
       <c r="F42" s="19"/>
       <c r="G42" s="20"/>
       <c r="H42" s="19"/>
@@ -2535,25 +2535,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="31"/>
-      <c r="L42" s="25"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="26"/>
-      <c r="T42" s="26"/>
-      <c r="U42" s="26"/>
-      <c r="V42" s="27"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="34"/>
+      <c r="N42" s="34"/>
+      <c r="O42" s="34"/>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="34"/>
+      <c r="S42" s="34"/>
+      <c r="T42" s="34"/>
+      <c r="U42" s="34"/>
+      <c r="V42" s="35"/>
     </row>
     <row r="43" spans="1:22" ht="23.1" customHeight="1">
       <c r="A43" s="23"/>
       <c r="B43" s="24"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="33"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="26"/>
       <c r="F43" s="19"/>
       <c r="G43" s="20"/>
       <c r="H43" s="19"/>
@@ -2562,18 +2562,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="31"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="26"/>
-      <c r="T43" s="26"/>
-      <c r="U43" s="26"/>
-      <c r="V43" s="27"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="33"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="34"/>
+      <c r="S43" s="34"/>
+      <c r="T43" s="34"/>
+      <c r="U43" s="34"/>
+      <c r="V43" s="35"/>
     </row>
     <row r="44" spans="1:22" ht="23.1" customHeight="1">
       <c r="A44" s="23"/>
@@ -2589,18 +2589,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K44" s="31"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="26"/>
-      <c r="O44" s="26"/>
-      <c r="P44" s="26"/>
-      <c r="Q44" s="26"/>
-      <c r="R44" s="26"/>
-      <c r="S44" s="26"/>
-      <c r="T44" s="26"/>
-      <c r="U44" s="26"/>
-      <c r="V44" s="27"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="33"/>
+      <c r="M44" s="34"/>
+      <c r="N44" s="34"/>
+      <c r="O44" s="34"/>
+      <c r="P44" s="34"/>
+      <c r="Q44" s="34"/>
+      <c r="R44" s="34"/>
+      <c r="S44" s="34"/>
+      <c r="T44" s="34"/>
+      <c r="U44" s="34"/>
+      <c r="V44" s="35"/>
     </row>
     <row r="45" spans="1:22" ht="23.1" customHeight="1">
       <c r="A45" s="9"/>
@@ -2627,131 +2627,276 @@
       <c r="V45" s="9"/>
     </row>
     <row r="46" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A46" s="28" t="s">
+      <c r="A46" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="30"/>
+      <c r="B46" s="105"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="105"/>
+      <c r="K46" s="105"/>
+      <c r="L46" s="105"/>
+      <c r="M46" s="105"/>
+      <c r="N46" s="105"/>
+      <c r="O46" s="105"/>
+      <c r="P46" s="105"/>
+      <c r="Q46" s="105"/>
+      <c r="R46" s="105"/>
+      <c r="S46" s="105"/>
+      <c r="T46" s="105"/>
+      <c r="U46" s="105"/>
+      <c r="V46" s="106"/>
     </row>
     <row r="47" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A47" s="102"/>
-      <c r="B47" s="103"/>
-      <c r="C47" s="103"/>
-      <c r="D47" s="103"/>
-      <c r="E47" s="103"/>
-      <c r="F47" s="103"/>
-      <c r="G47" s="103"/>
-      <c r="H47" s="103"/>
-      <c r="I47" s="103"/>
-      <c r="J47" s="103"/>
-      <c r="K47" s="103"/>
-      <c r="L47" s="103"/>
-      <c r="M47" s="103"/>
-      <c r="N47" s="103"/>
-      <c r="O47" s="103"/>
-      <c r="P47" s="103"/>
-      <c r="Q47" s="103"/>
-      <c r="R47" s="103"/>
-      <c r="S47" s="103"/>
-      <c r="T47" s="103"/>
-      <c r="U47" s="103"/>
-      <c r="V47" s="104"/>
+      <c r="A47" s="98"/>
+      <c r="B47" s="99"/>
+      <c r="C47" s="99"/>
+      <c r="D47" s="99"/>
+      <c r="E47" s="99"/>
+      <c r="F47" s="99"/>
+      <c r="G47" s="99"/>
+      <c r="H47" s="99"/>
+      <c r="I47" s="99"/>
+      <c r="J47" s="99"/>
+      <c r="K47" s="99"/>
+      <c r="L47" s="99"/>
+      <c r="M47" s="99"/>
+      <c r="N47" s="99"/>
+      <c r="O47" s="99"/>
+      <c r="P47" s="99"/>
+      <c r="Q47" s="99"/>
+      <c r="R47" s="99"/>
+      <c r="S47" s="99"/>
+      <c r="T47" s="99"/>
+      <c r="U47" s="99"/>
+      <c r="V47" s="100"/>
     </row>
     <row r="48" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A48" s="102"/>
-      <c r="B48" s="103"/>
-      <c r="C48" s="103"/>
-      <c r="D48" s="103"/>
-      <c r="E48" s="103"/>
-      <c r="F48" s="103"/>
-      <c r="G48" s="103"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="103"/>
-      <c r="J48" s="103"/>
-      <c r="K48" s="103"/>
-      <c r="L48" s="103"/>
-      <c r="M48" s="103"/>
-      <c r="N48" s="103"/>
-      <c r="O48" s="103"/>
-      <c r="P48" s="103"/>
-      <c r="Q48" s="103"/>
-      <c r="R48" s="103"/>
-      <c r="S48" s="103"/>
-      <c r="T48" s="103"/>
-      <c r="U48" s="103"/>
-      <c r="V48" s="104"/>
+      <c r="A48" s="98"/>
+      <c r="B48" s="99"/>
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="99"/>
+      <c r="I48" s="99"/>
+      <c r="J48" s="99"/>
+      <c r="K48" s="99"/>
+      <c r="L48" s="99"/>
+      <c r="M48" s="99"/>
+      <c r="N48" s="99"/>
+      <c r="O48" s="99"/>
+      <c r="P48" s="99"/>
+      <c r="Q48" s="99"/>
+      <c r="R48" s="99"/>
+      <c r="S48" s="99"/>
+      <c r="T48" s="99"/>
+      <c r="U48" s="99"/>
+      <c r="V48" s="100"/>
     </row>
     <row r="49" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A49" s="105"/>
-      <c r="B49" s="106"/>
-      <c r="C49" s="106"/>
-      <c r="D49" s="106"/>
-      <c r="E49" s="106"/>
-      <c r="F49" s="106"/>
-      <c r="G49" s="106"/>
-      <c r="H49" s="106"/>
-      <c r="I49" s="106"/>
-      <c r="J49" s="106"/>
-      <c r="K49" s="106"/>
-      <c r="L49" s="106"/>
-      <c r="M49" s="106"/>
-      <c r="N49" s="106"/>
-      <c r="O49" s="106"/>
-      <c r="P49" s="106"/>
-      <c r="Q49" s="106"/>
-      <c r="R49" s="106"/>
-      <c r="S49" s="106"/>
-      <c r="T49" s="106"/>
-      <c r="U49" s="106"/>
-      <c r="V49" s="107"/>
+      <c r="A49" s="101"/>
+      <c r="B49" s="102"/>
+      <c r="C49" s="102"/>
+      <c r="D49" s="102"/>
+      <c r="E49" s="102"/>
+      <c r="F49" s="102"/>
+      <c r="G49" s="102"/>
+      <c r="H49" s="102"/>
+      <c r="I49" s="102"/>
+      <c r="J49" s="102"/>
+      <c r="K49" s="102"/>
+      <c r="L49" s="102"/>
+      <c r="M49" s="102"/>
+      <c r="N49" s="102"/>
+      <c r="O49" s="102"/>
+      <c r="P49" s="102"/>
+      <c r="Q49" s="102"/>
+      <c r="R49" s="102"/>
+      <c r="S49" s="102"/>
+      <c r="T49" s="102"/>
+      <c r="U49" s="102"/>
+      <c r="V49" s="103"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="219">
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="L39:V39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="A47:V49"/>
+    <mergeCell ref="A46:V46"/>
+    <mergeCell ref="L44:V44"/>
+    <mergeCell ref="L43:V43"/>
+    <mergeCell ref="L42:V42"/>
+    <mergeCell ref="L41:V41"/>
+    <mergeCell ref="L40:V40"/>
+    <mergeCell ref="L34:V34"/>
+    <mergeCell ref="L33:V33"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="L35:V35"/>
+    <mergeCell ref="L36:V36"/>
+    <mergeCell ref="L37:V37"/>
+    <mergeCell ref="L38:V38"/>
+    <mergeCell ref="L21:V21"/>
+    <mergeCell ref="L22:V22"/>
+    <mergeCell ref="L23:V23"/>
+    <mergeCell ref="L24:V24"/>
+    <mergeCell ref="L25:V25"/>
+    <mergeCell ref="L26:V26"/>
+    <mergeCell ref="L27:V27"/>
+    <mergeCell ref="L28:V28"/>
+    <mergeCell ref="L29:V29"/>
+    <mergeCell ref="L32:V32"/>
+    <mergeCell ref="L31:V31"/>
+    <mergeCell ref="L30:V30"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="Q1:R2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="R4:T5"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="O4:Q5"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="S1:V2"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L13:V13"/>
+    <mergeCell ref="L14:V14"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="J11:K12"/>
+    <mergeCell ref="L11:V12"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="A15:B15"/>
@@ -2776,176 +2921,31 @@
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="H17:I17"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L13:V13"/>
-    <mergeCell ref="L14:V14"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="J11:K12"/>
-    <mergeCell ref="L11:V12"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="Q1:R2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="R4:T5"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="O4:Q5"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="S1:V2"/>
-    <mergeCell ref="L35:V35"/>
-    <mergeCell ref="L36:V36"/>
-    <mergeCell ref="L37:V37"/>
-    <mergeCell ref="L38:V38"/>
-    <mergeCell ref="L21:V21"/>
-    <mergeCell ref="L22:V22"/>
-    <mergeCell ref="L23:V23"/>
-    <mergeCell ref="L24:V24"/>
-    <mergeCell ref="L25:V25"/>
-    <mergeCell ref="L26:V26"/>
-    <mergeCell ref="L27:V27"/>
-    <mergeCell ref="L28:V28"/>
-    <mergeCell ref="L29:V29"/>
-    <mergeCell ref="L32:V32"/>
-    <mergeCell ref="L31:V31"/>
-    <mergeCell ref="L30:V30"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A47:V49"/>
-    <mergeCell ref="A46:V46"/>
-    <mergeCell ref="L44:V44"/>
-    <mergeCell ref="L43:V43"/>
-    <mergeCell ref="L42:V42"/>
-    <mergeCell ref="L41:V41"/>
-    <mergeCell ref="L40:V40"/>
-    <mergeCell ref="L34:V34"/>
-    <mergeCell ref="L33:V33"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="L39:V39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="F26:G26"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:J2 E8:G9">

--- a/public/work-report-default-template.xlsx
+++ b/public/work-report-default-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE6AEA65-7C64-45A6-906A-03449807D26B}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A5784BE-ECB3-434C-B90E-220F5CE37C9E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,25 +16,25 @@
     <sheet name="作業報告書" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_1ヶ月あたりの作業単位">作業報告書!$E$9</definedName>
-    <definedName name="_1日あたりの作業単位">作業報告書!$E$8</definedName>
+    <definedName name="_1ヶ月あたりの作業単位" localSheetId="0">作業報告書!$E$9</definedName>
+    <definedName name="_1日あたりの作業単位" localSheetId="0">作業報告書!$E$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">作業報告書!$A$1:$V$49</definedName>
-    <definedName name="タイトル">作業報告書!$A$1</definedName>
-    <definedName name="稼働時間">作業報告書!$J$14:$K$44</definedName>
+    <definedName name="タイトル" localSheetId="0">作業報告書!$A$1</definedName>
+    <definedName name="稼働時間列" localSheetId="0">作業報告書!$J$14:$K$44</definedName>
     <definedName name="稼働日数" localSheetId="0">作業報告書!$L$4</definedName>
-    <definedName name="開始時刻">作業報告書!$D$14:$E$44</definedName>
+    <definedName name="開始時刻列" localSheetId="0">作業報告書!$D$14:$E$44</definedName>
     <definedName name="基本稼働時間" localSheetId="0">作業報告書!$E$7</definedName>
-    <definedName name="基本開始時刻">作業報告書!$E$4</definedName>
-    <definedName name="基本休憩時間">作業報告書!$E$6</definedName>
-    <definedName name="基本終了時刻">作業報告書!$E$5</definedName>
-    <definedName name="休憩時間">作業報告書!$H$14:$I$44</definedName>
-    <definedName name="作業者名">作業報告書!$S$1</definedName>
-    <definedName name="作業内容">作業報告書!$L$14:$V$44</definedName>
-    <definedName name="終了時刻">作業報告書!$F$14:$G$44</definedName>
+    <definedName name="基本開始時刻" localSheetId="0">作業報告書!$E$4</definedName>
+    <definedName name="基本休憩時間" localSheetId="0">作業報告書!$E$6</definedName>
+    <definedName name="基本終了時刻" localSheetId="0">作業報告書!$E$5</definedName>
+    <definedName name="休憩時間列" localSheetId="0">作業報告書!$H$14:$I$44</definedName>
+    <definedName name="作業者名" localSheetId="0">作業報告書!$S$1</definedName>
+    <definedName name="作業内容列" localSheetId="0">作業報告書!$L$14:$V$44</definedName>
+    <definedName name="終了時刻列" localSheetId="0">作業報告書!$F$14:$G$44</definedName>
     <definedName name="総稼働時間" localSheetId="0">作業報告書!$R$4</definedName>
-    <definedName name="日付">作業報告書!$A$14:$B$44</definedName>
-    <definedName name="備考">作業報告書!$A$47</definedName>
-    <definedName name="曜日">作業報告書!$C$14:$C$44</definedName>
+    <definedName name="日付列" localSheetId="0">作業報告書!$A$14:$B$44</definedName>
+    <definedName name="備考" localSheetId="0">作業報告書!$A$47</definedName>
+    <definedName name="曜日列" localSheetId="0">作業報告書!$C$14:$C$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -790,7 +790,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -798,6 +798,54 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -806,6 +854,21 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -815,6 +878,187 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -823,250 +1067,6 @@
     </xf>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1446,54 +1446,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A1" s="74"/>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
+      <c r="A1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="77" t="s">
+      <c r="Q1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="78"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
     </row>
     <row r="2" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
-      <c r="V2" s="97"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
     </row>
     <row r="3" spans="1:22" ht="23.1" customHeight="1">
       <c r="A3" s="6"/>
@@ -1520,64 +1520,64 @@
       <c r="V3" s="7"/>
     </row>
     <row r="4" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="80" t="s">
+      <c r="I4" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="81"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="90"/>
-      <c r="O4" s="91" t="s">
+      <c r="J4" s="52"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="61"/>
+      <c r="O4" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="84"/>
-      <c r="T4" s="85"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="56"/>
       <c r="U4" s="7"/>
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="50"/>
       <c r="H5" s="12"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="95"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="88"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="58"/>
+      <c r="T5" s="59"/>
       <c r="U5" s="7"/>
       <c r="V5" s="16"/>
     </row>
     <row r="6" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="38"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
       <c r="H6" s="12"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -1593,15 +1593,15 @@
       <c r="V6" s="15"/>
     </row>
     <row r="7" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="32"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="107"/>
       <c r="H7" s="12"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -1618,28 +1618,28 @@
       <c r="V7" s="15"/>
     </row>
     <row r="8" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="62"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="93"/>
       <c r="H8" s="7"/>
       <c r="U8" s="7"/>
     </row>
     <row r="9" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="62"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="93"/>
       <c r="H9" s="7"/>
       <c r="O9" s="7"/>
       <c r="U9" s="7"/>
@@ -1670,134 +1670,134 @@
       <c r="V10" s="7"/>
     </row>
     <row r="11" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="49" t="s">
+      <c r="B11" s="94"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="49" t="s">
+      <c r="E11" s="81"/>
+      <c r="F11" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="50"/>
-      <c r="H11" s="49" t="s">
+      <c r="G11" s="81"/>
+      <c r="H11" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="50"/>
-      <c r="J11" s="53" t="s">
+      <c r="I11" s="81"/>
+      <c r="J11" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="54"/>
-      <c r="L11" s="53" t="s">
+      <c r="K11" s="85"/>
+      <c r="L11" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="57"/>
-      <c r="N11" s="57"/>
-      <c r="O11" s="57"/>
-      <c r="P11" s="57"/>
-      <c r="Q11" s="57"/>
-      <c r="R11" s="57"/>
-      <c r="S11" s="57"/>
-      <c r="T11" s="57"/>
-      <c r="U11" s="57"/>
-      <c r="V11" s="54"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="88"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="88"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="85"/>
     </row>
     <row r="12" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="58"/>
-      <c r="S12" s="58"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="58"/>
-      <c r="V12" s="56"/>
+      <c r="A12" s="96"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="87"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="89"/>
+      <c r="O12" s="89"/>
+      <c r="P12" s="89"/>
+      <c r="Q12" s="89"/>
+      <c r="R12" s="89"/>
+      <c r="S12" s="89"/>
+      <c r="T12" s="89"/>
+      <c r="U12" s="89"/>
+      <c r="V12" s="87"/>
     </row>
     <row r="13" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70">
+      <c r="B13" s="100"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="101">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E13" s="71"/>
-      <c r="F13" s="70">
+      <c r="E13" s="102"/>
+      <c r="F13" s="101">
         <v>0.79166666666666663</v>
       </c>
-      <c r="G13" s="71"/>
-      <c r="H13" s="72">
+      <c r="G13" s="102"/>
+      <c r="H13" s="103">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I13" s="73"/>
-      <c r="J13" s="70">
+      <c r="I13" s="104"/>
+      <c r="J13" s="101">
         <v>0.33333333333333331</v>
       </c>
-      <c r="K13" s="71"/>
-      <c r="L13" s="43" t="s">
+      <c r="K13" s="102"/>
+      <c r="L13" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="44"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
-      <c r="U13" s="44"/>
-      <c r="V13" s="45"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="75"/>
+      <c r="Q13" s="75"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="75"/>
+      <c r="V13" s="76"/>
     </row>
     <row r="14" spans="1:22" ht="23.1" customHeight="1">
       <c r="A14" s="23"/>
       <c r="B14" s="24"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
       <c r="F14" s="19"/>
       <c r="G14" s="20"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41" t="str">
+      <c r="H14" s="70"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72" t="str">
         <f t="shared" ref="J14" si="0">IF(D14="","",(ABS(F14-D14))-H14)</f>
         <v/>
       </c>
-      <c r="K14" s="42"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="48"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="78"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="78"/>
+      <c r="U14" s="78"/>
+      <c r="V14" s="79"/>
     </row>
     <row r="15" spans="1:22" ht="23.1" customHeight="1">
       <c r="A15" s="23"/>
       <c r="B15" s="24"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="26"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="39"/>
       <c r="F15" s="19"/>
       <c r="G15" s="20"/>
       <c r="H15" s="19"/>
@@ -1806,25 +1806,25 @@
         <f t="shared" ref="J15:J44" si="1">IF(D15="","",(ABS(F15-D15))-H15)</f>
         <v/>
       </c>
-      <c r="K15" s="22"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="35"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="27"/>
     </row>
     <row r="16" spans="1:22" ht="23.1" customHeight="1">
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="26"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="39"/>
       <c r="F16" s="19"/>
       <c r="G16" s="20"/>
       <c r="H16" s="19"/>
@@ -1833,79 +1833,79 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K16" s="22"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="35"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="27"/>
     </row>
     <row r="17" spans="1:22" ht="23.1" customHeight="1">
       <c r="A17" s="23"/>
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="26"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
       <c r="H17" s="19"/>
       <c r="I17" s="20"/>
       <c r="J17" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="22"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="35"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="26"/>
+      <c r="U17" s="26"/>
+      <c r="V17" s="27"/>
     </row>
     <row r="18" spans="1:22" ht="23.1" customHeight="1">
       <c r="A18" s="23"/>
       <c r="B18" s="24"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="26"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="19"/>
       <c r="I18" s="20"/>
       <c r="J18" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="22"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="35"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="26"/>
+      <c r="U18" s="26"/>
+      <c r="V18" s="27"/>
     </row>
     <row r="19" spans="1:22" ht="23.1" customHeight="1">
       <c r="A19" s="23"/>
       <c r="B19" s="24"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="39"/>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
       <c r="H19" s="19"/>
@@ -1914,25 +1914,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="22"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="35"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="26"/>
+      <c r="U19" s="26"/>
+      <c r="V19" s="27"/>
     </row>
     <row r="20" spans="1:22" ht="23.1" customHeight="1">
       <c r="A20" s="23"/>
       <c r="B20" s="24"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="26"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="39"/>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="19"/>
@@ -1941,25 +1941,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="22"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="35"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="26"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="26"/>
+      <c r="V20" s="27"/>
     </row>
     <row r="21" spans="1:22" ht="23.1" customHeight="1">
       <c r="A21" s="23"/>
       <c r="B21" s="24"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="26"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="39"/>
       <c r="F21" s="19"/>
       <c r="G21" s="20"/>
       <c r="H21" s="19"/>
@@ -1968,25 +1968,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="22"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="34"/>
-      <c r="V21" s="35"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
+      <c r="S21" s="26"/>
+      <c r="T21" s="26"/>
+      <c r="U21" s="26"/>
+      <c r="V21" s="27"/>
     </row>
     <row r="22" spans="1:22" ht="23.1" customHeight="1">
       <c r="A22" s="23"/>
       <c r="B22" s="24"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="39"/>
       <c r="F22" s="19"/>
       <c r="G22" s="20"/>
       <c r="H22" s="19"/>
@@ -1995,25 +1995,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="22"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="34"/>
-      <c r="V22" s="35"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="27"/>
     </row>
     <row r="23" spans="1:22" ht="23.1" customHeight="1">
       <c r="A23" s="23"/>
       <c r="B23" s="24"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="26"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="39"/>
       <c r="F23" s="19"/>
       <c r="G23" s="20"/>
       <c r="H23" s="19"/>
@@ -2022,18 +2022,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="22"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="34"/>
-      <c r="V23" s="35"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="26"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="26"/>
+      <c r="V23" s="27"/>
     </row>
     <row r="24" spans="1:22" ht="23.1" customHeight="1">
       <c r="A24" s="23"/>
@@ -2049,18 +2049,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="22"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34"/>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="34"/>
-      <c r="V24" s="35"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="26"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="26"/>
+      <c r="V24" s="27"/>
     </row>
     <row r="25" spans="1:22" ht="23.1" customHeight="1">
       <c r="A25" s="23"/>
@@ -2076,25 +2076,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="22"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="35"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="26"/>
+      <c r="U25" s="26"/>
+      <c r="V25" s="27"/>
     </row>
     <row r="26" spans="1:22" ht="23.1" customHeight="1">
       <c r="A26" s="23"/>
       <c r="B26" s="24"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="26"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="39"/>
       <c r="F26" s="19"/>
       <c r="G26" s="20"/>
       <c r="H26" s="19"/>
@@ -2103,25 +2103,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="22"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="34"/>
-      <c r="V26" s="35"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="27"/>
     </row>
     <row r="27" spans="1:22" ht="23.1" customHeight="1">
       <c r="A27" s="23"/>
       <c r="B27" s="24"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="26"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="39"/>
       <c r="F27" s="19"/>
       <c r="G27" s="20"/>
       <c r="H27" s="19"/>
@@ -2130,25 +2130,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="22"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="34"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="34"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="35"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="27"/>
     </row>
     <row r="28" spans="1:22" ht="23.1" customHeight="1">
       <c r="A28" s="23"/>
       <c r="B28" s="24"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="26"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="39"/>
       <c r="F28" s="19"/>
       <c r="G28" s="20"/>
       <c r="H28" s="19"/>
@@ -2157,25 +2157,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="34"/>
-      <c r="V28" s="35"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="27"/>
     </row>
     <row r="29" spans="1:22" ht="23.1" customHeight="1">
       <c r="A29" s="23"/>
       <c r="B29" s="24"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="26"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="39"/>
       <c r="F29" s="19"/>
       <c r="G29" s="20"/>
       <c r="H29" s="19"/>
@@ -2184,25 +2184,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="22"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="34"/>
-      <c r="R29" s="34"/>
-      <c r="S29" s="34"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="35"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="26"/>
+      <c r="T29" s="26"/>
+      <c r="U29" s="26"/>
+      <c r="V29" s="27"/>
     </row>
     <row r="30" spans="1:22" ht="23.1" customHeight="1">
       <c r="A30" s="23"/>
       <c r="B30" s="24"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="26"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="39"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="19"/>
@@ -2211,18 +2211,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="22"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="34"/>
-      <c r="V30" s="35"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="27"/>
     </row>
     <row r="31" spans="1:22" ht="23.1" customHeight="1">
       <c r="A31" s="23"/>
@@ -2238,18 +2238,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="22"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="35"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26"/>
+      <c r="V31" s="27"/>
     </row>
     <row r="32" spans="1:22" ht="23.1" customHeight="1">
       <c r="A32" s="23"/>
@@ -2265,18 +2265,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="22"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="34"/>
-      <c r="V32" s="35"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="27"/>
     </row>
     <row r="33" spans="1:22" ht="23.1" customHeight="1">
       <c r="A33" s="23"/>
@@ -2292,25 +2292,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="22"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="34"/>
-      <c r="V33" s="35"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="26"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="27"/>
     </row>
     <row r="34" spans="1:22" ht="23.1" customHeight="1">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="26"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="39"/>
       <c r="F34" s="19"/>
       <c r="G34" s="20"/>
       <c r="H34" s="19"/>
@@ -2319,25 +2319,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="22"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="35"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="26"/>
+      <c r="T34" s="26"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="27"/>
     </row>
     <row r="35" spans="1:22" ht="23.1" customHeight="1">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="26"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="39"/>
       <c r="F35" s="19"/>
       <c r="G35" s="20"/>
       <c r="H35" s="19"/>
@@ -2346,25 +2346,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="34"/>
-      <c r="V35" s="35"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="26"/>
+      <c r="S35" s="26"/>
+      <c r="T35" s="26"/>
+      <c r="U35" s="26"/>
+      <c r="V35" s="27"/>
     </row>
     <row r="36" spans="1:22" ht="23.1" customHeight="1">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="26"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="39"/>
       <c r="F36" s="19"/>
       <c r="G36" s="20"/>
       <c r="H36" s="19"/>
@@ -2373,25 +2373,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="22"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="35"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="26"/>
+      <c r="U36" s="26"/>
+      <c r="V36" s="27"/>
     </row>
     <row r="37" spans="1:22" ht="23.1" customHeight="1">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="26"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="39"/>
       <c r="F37" s="19"/>
       <c r="G37" s="20"/>
       <c r="H37" s="19"/>
@@ -2400,18 +2400,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="22"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="34"/>
-      <c r="V37" s="35"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="26"/>
+      <c r="S37" s="26"/>
+      <c r="T37" s="26"/>
+      <c r="U37" s="26"/>
+      <c r="V37" s="27"/>
     </row>
     <row r="38" spans="1:22" ht="23.1" customHeight="1">
       <c r="A38" s="23"/>
@@ -2427,18 +2427,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="22"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="34"/>
-      <c r="V38" s="35"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
+      <c r="S38" s="26"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="26"/>
+      <c r="V38" s="27"/>
     </row>
     <row r="39" spans="1:22" ht="23.1" customHeight="1">
       <c r="A39" s="23"/>
@@ -2454,18 +2454,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="107"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="35"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="26"/>
+      <c r="S39" s="26"/>
+      <c r="T39" s="26"/>
+      <c r="U39" s="26"/>
+      <c r="V39" s="27"/>
     </row>
     <row r="40" spans="1:22" ht="23.1" customHeight="1">
       <c r="A40" s="23"/>
@@ -2481,18 +2481,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="107"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="34"/>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="34"/>
-      <c r="V40" s="35"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+      <c r="P40" s="26"/>
+      <c r="Q40" s="26"/>
+      <c r="R40" s="26"/>
+      <c r="S40" s="26"/>
+      <c r="T40" s="26"/>
+      <c r="U40" s="26"/>
+      <c r="V40" s="27"/>
     </row>
     <row r="41" spans="1:22" ht="23.1" customHeight="1">
       <c r="A41" s="23"/>
@@ -2508,25 +2508,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="107"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="34"/>
-      <c r="N41" s="34"/>
-      <c r="O41" s="34"/>
-      <c r="P41" s="34"/>
-      <c r="Q41" s="34"/>
-      <c r="R41" s="34"/>
-      <c r="S41" s="34"/>
-      <c r="T41" s="34"/>
-      <c r="U41" s="34"/>
-      <c r="V41" s="35"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="25"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="26"/>
+      <c r="S41" s="26"/>
+      <c r="T41" s="26"/>
+      <c r="U41" s="26"/>
+      <c r="V41" s="27"/>
     </row>
     <row r="42" spans="1:22" ht="23.1" customHeight="1">
       <c r="A42" s="23"/>
       <c r="B42" s="24"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="26"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="39"/>
       <c r="F42" s="19"/>
       <c r="G42" s="20"/>
       <c r="H42" s="19"/>
@@ -2535,25 +2535,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="22"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="34"/>
-      <c r="N42" s="34"/>
-      <c r="O42" s="34"/>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="34"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="34"/>
-      <c r="U42" s="34"/>
-      <c r="V42" s="35"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="26"/>
+      <c r="T42" s="26"/>
+      <c r="U42" s="26"/>
+      <c r="V42" s="27"/>
     </row>
     <row r="43" spans="1:22" ht="23.1" customHeight="1">
       <c r="A43" s="23"/>
       <c r="B43" s="24"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="26"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="39"/>
       <c r="F43" s="19"/>
       <c r="G43" s="20"/>
       <c r="H43" s="19"/>
@@ -2562,18 +2562,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="22"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="34"/>
-      <c r="N43" s="34"/>
-      <c r="O43" s="34"/>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="34"/>
-      <c r="R43" s="34"/>
-      <c r="S43" s="34"/>
-      <c r="T43" s="34"/>
-      <c r="U43" s="34"/>
-      <c r="V43" s="35"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="25"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="26"/>
+      <c r="S43" s="26"/>
+      <c r="T43" s="26"/>
+      <c r="U43" s="26"/>
+      <c r="V43" s="27"/>
     </row>
     <row r="44" spans="1:22" ht="23.1" customHeight="1">
       <c r="A44" s="23"/>
@@ -2589,18 +2589,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K44" s="22"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="34"/>
-      <c r="N44" s="34"/>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-      <c r="U44" s="34"/>
-      <c r="V44" s="35"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="26"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="26"/>
+      <c r="S44" s="26"/>
+      <c r="T44" s="26"/>
+      <c r="U44" s="26"/>
+      <c r="V44" s="27"/>
     </row>
     <row r="45" spans="1:22" ht="23.1" customHeight="1">
       <c r="A45" s="9"/>
@@ -2627,122 +2627,285 @@
       <c r="V45" s="9"/>
     </row>
     <row r="46" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A46" s="104" t="s">
+      <c r="A46" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="105"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="105"/>
-      <c r="I46" s="105"/>
-      <c r="J46" s="105"/>
-      <c r="K46" s="105"/>
-      <c r="L46" s="105"/>
-      <c r="M46" s="105"/>
-      <c r="N46" s="105"/>
-      <c r="O46" s="105"/>
-      <c r="P46" s="105"/>
-      <c r="Q46" s="105"/>
-      <c r="R46" s="105"/>
-      <c r="S46" s="105"/>
-      <c r="T46" s="105"/>
-      <c r="U46" s="105"/>
-      <c r="V46" s="106"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="35"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="35"/>
+      <c r="V46" s="36"/>
     </row>
     <row r="47" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A47" s="98"/>
-      <c r="B47" s="99"/>
-      <c r="C47" s="99"/>
-      <c r="D47" s="99"/>
-      <c r="E47" s="99"/>
-      <c r="F47" s="99"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="99"/>
-      <c r="I47" s="99"/>
-      <c r="J47" s="99"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="99"/>
-      <c r="N47" s="99"/>
-      <c r="O47" s="99"/>
-      <c r="P47" s="99"/>
-      <c r="Q47" s="99"/>
-      <c r="R47" s="99"/>
-      <c r="S47" s="99"/>
-      <c r="T47" s="99"/>
-      <c r="U47" s="99"/>
-      <c r="V47" s="100"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+      <c r="T47" s="29"/>
+      <c r="U47" s="29"/>
+      <c r="V47" s="30"/>
     </row>
     <row r="48" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A48" s="98"/>
-      <c r="B48" s="99"/>
-      <c r="C48" s="99"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
-      <c r="H48" s="99"/>
-      <c r="I48" s="99"/>
-      <c r="J48" s="99"/>
-      <c r="K48" s="99"/>
-      <c r="L48" s="99"/>
-      <c r="M48" s="99"/>
-      <c r="N48" s="99"/>
-      <c r="O48" s="99"/>
-      <c r="P48" s="99"/>
-      <c r="Q48" s="99"/>
-      <c r="R48" s="99"/>
-      <c r="S48" s="99"/>
-      <c r="T48" s="99"/>
-      <c r="U48" s="99"/>
-      <c r="V48" s="100"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="29"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="30"/>
     </row>
     <row r="49" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A49" s="101"/>
-      <c r="B49" s="102"/>
-      <c r="C49" s="102"/>
-      <c r="D49" s="102"/>
-      <c r="E49" s="102"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="102"/>
-      <c r="H49" s="102"/>
-      <c r="I49" s="102"/>
-      <c r="J49" s="102"/>
-      <c r="K49" s="102"/>
-      <c r="L49" s="102"/>
-      <c r="M49" s="102"/>
-      <c r="N49" s="102"/>
-      <c r="O49" s="102"/>
-      <c r="P49" s="102"/>
-      <c r="Q49" s="102"/>
-      <c r="R49" s="102"/>
-      <c r="S49" s="102"/>
-      <c r="T49" s="102"/>
-      <c r="U49" s="102"/>
-      <c r="V49" s="103"/>
+      <c r="A49" s="31"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="33"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="219">
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="L39:V39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L20:V20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="L19:V19"/>
+    <mergeCell ref="L18:V18"/>
+    <mergeCell ref="L17:V17"/>
+    <mergeCell ref="L16:V16"/>
+    <mergeCell ref="L15:V15"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L13:V13"/>
+    <mergeCell ref="L14:V14"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="J11:K12"/>
+    <mergeCell ref="L11:V12"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="Q1:R2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="R4:T5"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="O4:Q5"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="S1:V2"/>
+    <mergeCell ref="L35:V35"/>
+    <mergeCell ref="L36:V36"/>
+    <mergeCell ref="L37:V37"/>
+    <mergeCell ref="L38:V38"/>
+    <mergeCell ref="L21:V21"/>
+    <mergeCell ref="L22:V22"/>
+    <mergeCell ref="L23:V23"/>
+    <mergeCell ref="L24:V24"/>
+    <mergeCell ref="L25:V25"/>
+    <mergeCell ref="L26:V26"/>
+    <mergeCell ref="L27:V27"/>
+    <mergeCell ref="L28:V28"/>
+    <mergeCell ref="L29:V29"/>
+    <mergeCell ref="L32:V32"/>
+    <mergeCell ref="L31:V31"/>
+    <mergeCell ref="L30:V30"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="A47:V49"/>
     <mergeCell ref="A46:V46"/>
     <mergeCell ref="L44:V44"/>
@@ -2767,185 +2930,22 @@
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="H43:I43"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="L35:V35"/>
-    <mergeCell ref="L36:V36"/>
-    <mergeCell ref="L37:V37"/>
-    <mergeCell ref="L38:V38"/>
-    <mergeCell ref="L21:V21"/>
-    <mergeCell ref="L22:V22"/>
-    <mergeCell ref="L23:V23"/>
-    <mergeCell ref="L24:V24"/>
-    <mergeCell ref="L25:V25"/>
-    <mergeCell ref="L26:V26"/>
-    <mergeCell ref="L27:V27"/>
-    <mergeCell ref="L28:V28"/>
-    <mergeCell ref="L29:V29"/>
-    <mergeCell ref="L32:V32"/>
-    <mergeCell ref="L31:V31"/>
-    <mergeCell ref="L30:V30"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="Q1:R2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="R4:T5"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="O4:Q5"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="S1:V2"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L13:V13"/>
-    <mergeCell ref="L14:V14"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="J11:K12"/>
-    <mergeCell ref="L11:V12"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L20:V20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="L19:V19"/>
-    <mergeCell ref="L18:V18"/>
-    <mergeCell ref="L17:V17"/>
-    <mergeCell ref="L16:V16"/>
-    <mergeCell ref="L15:V15"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="L39:V39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J39:K39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:J2 E8:G9">

--- a/public/work-report-default-template.xlsx
+++ b/public/work-report-default-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A5784BE-ECB3-434C-B90E-220F5CE37C9E}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D92179C-F5D4-4F55-BE38-57F841DDF9FA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,12 +28,12 @@
     <definedName name="基本休憩時間" localSheetId="0">作業報告書!$E$6</definedName>
     <definedName name="基本終了時刻" localSheetId="0">作業報告書!$E$5</definedName>
     <definedName name="休憩時間列" localSheetId="0">作業報告書!$H$14:$I$44</definedName>
-    <definedName name="作業者名" localSheetId="0">作業報告書!$S$1</definedName>
     <definedName name="作業内容列" localSheetId="0">作業報告書!$L$14:$V$44</definedName>
     <definedName name="終了時刻列" localSheetId="0">作業報告書!$F$14:$G$44</definedName>
     <definedName name="総稼働時間" localSheetId="0">作業報告書!$R$4</definedName>
     <definedName name="日付列" localSheetId="0">作業報告書!$A$14:$B$44</definedName>
     <definedName name="備考" localSheetId="0">作業報告書!$A$47</definedName>
+    <definedName name="名前" localSheetId="0">作業報告書!$S$1</definedName>
     <definedName name="曜日列" localSheetId="0">作業報告書!$C$14:$C$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -790,7 +790,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -798,6 +798,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
@@ -810,6 +836,202 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -844,229 +1066,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1446,54 +1446,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A1" s="40"/>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
+      <c r="A1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="43" t="s">
+      <c r="Q1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="44"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
     </row>
     <row r="2" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
     </row>
     <row r="3" spans="1:22" ht="23.1" customHeight="1">
       <c r="A3" s="6"/>
@@ -1520,64 +1520,64 @@
       <c r="V3" s="7"/>
     </row>
     <row r="4" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="52"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="61"/>
-      <c r="O4" s="62" t="s">
+      <c r="J4" s="81"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="90"/>
+      <c r="O4" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="56"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="84"/>
+      <c r="T4" s="85"/>
       <c r="U4" s="7"/>
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="50"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38"/>
       <c r="H5" s="12"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="57"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="59"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="86"/>
+      <c r="S5" s="87"/>
+      <c r="T5" s="88"/>
       <c r="U5" s="7"/>
       <c r="V5" s="16"/>
     </row>
     <row r="6" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
       <c r="H6" s="12"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -1593,15 +1593,15 @@
       <c r="V6" s="15"/>
     </row>
     <row r="7" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="107"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="32"/>
       <c r="H7" s="12"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -1618,28 +1618,28 @@
       <c r="V7" s="15"/>
     </row>
     <row r="8" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="93"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="62"/>
       <c r="H8" s="7"/>
       <c r="U8" s="7"/>
     </row>
     <row r="9" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="93"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="62"/>
       <c r="H9" s="7"/>
       <c r="O9" s="7"/>
       <c r="U9" s="7"/>
@@ -1670,134 +1670,134 @@
       <c r="V10" s="7"/>
     </row>
     <row r="11" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="94"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="80" t="s">
+      <c r="B11" s="63"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="80" t="s">
+      <c r="E11" s="50"/>
+      <c r="F11" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="81"/>
-      <c r="H11" s="80" t="s">
+      <c r="G11" s="50"/>
+      <c r="H11" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="81"/>
-      <c r="J11" s="84" t="s">
+      <c r="I11" s="50"/>
+      <c r="J11" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="85"/>
-      <c r="L11" s="84" t="s">
+      <c r="K11" s="54"/>
+      <c r="L11" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="88"/>
-      <c r="N11" s="88"/>
-      <c r="O11" s="88"/>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="85"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="57"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="57"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="57"/>
+      <c r="V11" s="54"/>
     </row>
     <row r="12" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A12" s="96"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="87"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="89"/>
-      <c r="N12" s="89"/>
-      <c r="O12" s="89"/>
-      <c r="P12" s="89"/>
-      <c r="Q12" s="89"/>
-      <c r="R12" s="89"/>
-      <c r="S12" s="89"/>
-      <c r="T12" s="89"/>
-      <c r="U12" s="89"/>
-      <c r="V12" s="87"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="58"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="58"/>
+      <c r="S12" s="58"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="58"/>
+      <c r="V12" s="56"/>
     </row>
     <row r="13" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A13" s="99" t="s">
+      <c r="A13" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="100"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="101">
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="101">
+      <c r="E13" s="71"/>
+      <c r="F13" s="70">
         <v>0.79166666666666663</v>
       </c>
-      <c r="G13" s="102"/>
-      <c r="H13" s="103">
+      <c r="G13" s="71"/>
+      <c r="H13" s="72">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I13" s="104"/>
-      <c r="J13" s="101">
+      <c r="I13" s="73"/>
+      <c r="J13" s="70">
         <v>0.33333333333333331</v>
       </c>
-      <c r="K13" s="102"/>
-      <c r="L13" s="74" t="s">
+      <c r="K13" s="71"/>
+      <c r="L13" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="75"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="75"/>
-      <c r="V13" s="76"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="45"/>
     </row>
     <row r="14" spans="1:22" ht="23.1" customHeight="1">
       <c r="A14" s="23"/>
       <c r="B14" s="24"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="39"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="26"/>
       <c r="F14" s="19"/>
       <c r="G14" s="20"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="72" t="str">
+      <c r="H14" s="39"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="41" t="str">
         <f t="shared" ref="J14" si="0">IF(D14="","",(ABS(F14-D14))-H14)</f>
         <v/>
       </c>
-      <c r="K14" s="73"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="78"/>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="78"/>
-      <c r="U14" s="78"/>
-      <c r="V14" s="79"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="48"/>
     </row>
     <row r="15" spans="1:22" ht="23.1" customHeight="1">
       <c r="A15" s="23"/>
       <c r="B15" s="24"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="39"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="19"/>
       <c r="G15" s="20"/>
       <c r="H15" s="19"/>
@@ -1806,25 +1806,25 @@
         <f t="shared" ref="J15:J44" si="1">IF(D15="","",(ABS(F15-D15))-H15)</f>
         <v/>
       </c>
-      <c r="K15" s="37"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
-      <c r="V15" s="27"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="34"/>
+      <c r="V15" s="35"/>
     </row>
     <row r="16" spans="1:22" ht="23.1" customHeight="1">
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="39"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="26"/>
       <c r="F16" s="19"/>
       <c r="G16" s="20"/>
       <c r="H16" s="19"/>
@@ -1833,79 +1833,79 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K16" s="37"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="26"/>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="27"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="35"/>
     </row>
     <row r="17" spans="1:22" ht="23.1" customHeight="1">
       <c r="A17" s="23"/>
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="39"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="26"/>
       <c r="H17" s="19"/>
       <c r="I17" s="20"/>
       <c r="J17" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="37"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="26"/>
-      <c r="S17" s="26"/>
-      <c r="T17" s="26"/>
-      <c r="U17" s="26"/>
-      <c r="V17" s="27"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="35"/>
     </row>
     <row r="18" spans="1:22" ht="23.1" customHeight="1">
       <c r="A18" s="23"/>
       <c r="B18" s="24"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="26"/>
       <c r="H18" s="19"/>
       <c r="I18" s="20"/>
       <c r="J18" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="37"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-      <c r="V18" s="27"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="34"/>
+      <c r="V18" s="35"/>
     </row>
     <row r="19" spans="1:22" ht="23.1" customHeight="1">
       <c r="A19" s="23"/>
       <c r="B19" s="24"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="39"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
       <c r="H19" s="19"/>
@@ -1914,25 +1914,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="37"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-      <c r="V19" s="27"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="34"/>
+      <c r="V19" s="35"/>
     </row>
     <row r="20" spans="1:22" ht="23.1" customHeight="1">
       <c r="A20" s="23"/>
       <c r="B20" s="24"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="39"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="19"/>
@@ -1941,25 +1941,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="37"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-      <c r="V20" s="27"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="35"/>
     </row>
     <row r="21" spans="1:22" ht="23.1" customHeight="1">
       <c r="A21" s="23"/>
       <c r="B21" s="24"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="39"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="19"/>
       <c r="G21" s="20"/>
       <c r="H21" s="19"/>
@@ -1968,25 +1968,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="37"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="27"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="34"/>
+      <c r="V21" s="35"/>
     </row>
     <row r="22" spans="1:22" ht="23.1" customHeight="1">
       <c r="A22" s="23"/>
       <c r="B22" s="24"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="39"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
       <c r="F22" s="19"/>
       <c r="G22" s="20"/>
       <c r="H22" s="19"/>
@@ -1995,25 +1995,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="37"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-      <c r="V22" s="27"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="35"/>
     </row>
     <row r="23" spans="1:22" ht="23.1" customHeight="1">
       <c r="A23" s="23"/>
       <c r="B23" s="24"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="39"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="26"/>
       <c r="F23" s="19"/>
       <c r="G23" s="20"/>
       <c r="H23" s="19"/>
@@ -2022,18 +2022,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="37"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="27"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="35"/>
     </row>
     <row r="24" spans="1:22" ht="23.1" customHeight="1">
       <c r="A24" s="23"/>
@@ -2049,18 +2049,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="37"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="27"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34"/>
+      <c r="S24" s="34"/>
+      <c r="T24" s="34"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="35"/>
     </row>
     <row r="25" spans="1:22" ht="23.1" customHeight="1">
       <c r="A25" s="23"/>
@@ -2076,25 +2076,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="37"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="26"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
-      <c r="V25" s="27"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="34"/>
+      <c r="S25" s="34"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="34"/>
+      <c r="V25" s="35"/>
     </row>
     <row r="26" spans="1:22" ht="23.1" customHeight="1">
       <c r="A26" s="23"/>
       <c r="B26" s="24"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="39"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="26"/>
       <c r="F26" s="19"/>
       <c r="G26" s="20"/>
       <c r="H26" s="19"/>
@@ -2103,25 +2103,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="37"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="27"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
+      <c r="S26" s="34"/>
+      <c r="T26" s="34"/>
+      <c r="U26" s="34"/>
+      <c r="V26" s="35"/>
     </row>
     <row r="27" spans="1:22" ht="23.1" customHeight="1">
       <c r="A27" s="23"/>
       <c r="B27" s="24"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="19"/>
       <c r="G27" s="20"/>
       <c r="H27" s="19"/>
@@ -2130,25 +2130,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="37"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="27"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="34"/>
+      <c r="S27" s="34"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="34"/>
+      <c r="V27" s="35"/>
     </row>
     <row r="28" spans="1:22" ht="23.1" customHeight="1">
       <c r="A28" s="23"/>
       <c r="B28" s="24"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="39"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
       <c r="F28" s="19"/>
       <c r="G28" s="20"/>
       <c r="H28" s="19"/>
@@ -2157,25 +2157,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="37"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="27"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="34"/>
+      <c r="V28" s="35"/>
     </row>
     <row r="29" spans="1:22" ht="23.1" customHeight="1">
       <c r="A29" s="23"/>
       <c r="B29" s="24"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="39"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="19"/>
       <c r="G29" s="20"/>
       <c r="H29" s="19"/>
@@ -2184,25 +2184,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="37"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="27"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="U29" s="34"/>
+      <c r="V29" s="35"/>
     </row>
     <row r="30" spans="1:22" ht="23.1" customHeight="1">
       <c r="A30" s="23"/>
       <c r="B30" s="24"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="39"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="26"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="19"/>
@@ -2211,18 +2211,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="37"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="27"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="35"/>
     </row>
     <row r="31" spans="1:22" ht="23.1" customHeight="1">
       <c r="A31" s="23"/>
@@ -2238,18 +2238,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="37"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="27"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="35"/>
     </row>
     <row r="32" spans="1:22" ht="23.1" customHeight="1">
       <c r="A32" s="23"/>
@@ -2265,18 +2265,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="37"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="27"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="V32" s="35"/>
     </row>
     <row r="33" spans="1:22" ht="23.1" customHeight="1">
       <c r="A33" s="23"/>
@@ -2292,25 +2292,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="37"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="27"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="34"/>
+      <c r="S33" s="34"/>
+      <c r="T33" s="34"/>
+      <c r="U33" s="34"/>
+      <c r="V33" s="35"/>
     </row>
     <row r="34" spans="1:22" ht="23.1" customHeight="1">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="39"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
       <c r="F34" s="19"/>
       <c r="G34" s="20"/>
       <c r="H34" s="19"/>
@@ -2319,25 +2319,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="37"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="27"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
+      <c r="P34" s="34"/>
+      <c r="Q34" s="34"/>
+      <c r="R34" s="34"/>
+      <c r="S34" s="34"/>
+      <c r="T34" s="34"/>
+      <c r="U34" s="34"/>
+      <c r="V34" s="35"/>
     </row>
     <row r="35" spans="1:22" ht="23.1" customHeight="1">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="39"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="26"/>
       <c r="F35" s="19"/>
       <c r="G35" s="20"/>
       <c r="H35" s="19"/>
@@ -2346,25 +2346,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="37"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="26"/>
-      <c r="V35" s="27"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="34"/>
+      <c r="S35" s="34"/>
+      <c r="T35" s="34"/>
+      <c r="U35" s="34"/>
+      <c r="V35" s="35"/>
     </row>
     <row r="36" spans="1:22" ht="23.1" customHeight="1">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="26"/>
       <c r="F36" s="19"/>
       <c r="G36" s="20"/>
       <c r="H36" s="19"/>
@@ -2373,25 +2373,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="37"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="26"/>
-      <c r="V36" s="27"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="34"/>
+      <c r="P36" s="34"/>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="34"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="34"/>
+      <c r="U36" s="34"/>
+      <c r="V36" s="35"/>
     </row>
     <row r="37" spans="1:22" ht="23.1" customHeight="1">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="39"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="26"/>
       <c r="F37" s="19"/>
       <c r="G37" s="20"/>
       <c r="H37" s="19"/>
@@ -2400,18 +2400,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="37"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="26"/>
-      <c r="V37" s="27"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="34"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="34"/>
+      <c r="R37" s="34"/>
+      <c r="S37" s="34"/>
+      <c r="T37" s="34"/>
+      <c r="U37" s="34"/>
+      <c r="V37" s="35"/>
     </row>
     <row r="38" spans="1:22" ht="23.1" customHeight="1">
       <c r="A38" s="23"/>
@@ -2427,18 +2427,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="37"/>
-      <c r="L38" s="25"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="27"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="34"/>
+      <c r="N38" s="34"/>
+      <c r="O38" s="34"/>
+      <c r="P38" s="34"/>
+      <c r="Q38" s="34"/>
+      <c r="R38" s="34"/>
+      <c r="S38" s="34"/>
+      <c r="T38" s="34"/>
+      <c r="U38" s="34"/>
+      <c r="V38" s="35"/>
     </row>
     <row r="39" spans="1:22" ht="23.1" customHeight="1">
       <c r="A39" s="23"/>
@@ -2454,18 +2454,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="22"/>
-      <c r="L39" s="25"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="26"/>
-      <c r="O39" s="26"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26"/>
-      <c r="S39" s="26"/>
-      <c r="T39" s="26"/>
-      <c r="U39" s="26"/>
-      <c r="V39" s="27"/>
+      <c r="K39" s="107"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="34"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="34"/>
+      <c r="P39" s="34"/>
+      <c r="Q39" s="34"/>
+      <c r="R39" s="34"/>
+      <c r="S39" s="34"/>
+      <c r="T39" s="34"/>
+      <c r="U39" s="34"/>
+      <c r="V39" s="35"/>
     </row>
     <row r="40" spans="1:22" ht="23.1" customHeight="1">
       <c r="A40" s="23"/>
@@ -2481,18 +2481,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="25"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="26"/>
-      <c r="Q40" s="26"/>
-      <c r="R40" s="26"/>
-      <c r="S40" s="26"/>
-      <c r="T40" s="26"/>
-      <c r="U40" s="26"/>
-      <c r="V40" s="27"/>
+      <c r="K40" s="107"/>
+      <c r="L40" s="33"/>
+      <c r="M40" s="34"/>
+      <c r="N40" s="34"/>
+      <c r="O40" s="34"/>
+      <c r="P40" s="34"/>
+      <c r="Q40" s="34"/>
+      <c r="R40" s="34"/>
+      <c r="S40" s="34"/>
+      <c r="T40" s="34"/>
+      <c r="U40" s="34"/>
+      <c r="V40" s="35"/>
     </row>
     <row r="41" spans="1:22" ht="23.1" customHeight="1">
       <c r="A41" s="23"/>
@@ -2508,25 +2508,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="22"/>
-      <c r="L41" s="25"/>
-      <c r="M41" s="26"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="26"/>
-      <c r="P41" s="26"/>
-      <c r="Q41" s="26"/>
-      <c r="R41" s="26"/>
-      <c r="S41" s="26"/>
-      <c r="T41" s="26"/>
-      <c r="U41" s="26"/>
-      <c r="V41" s="27"/>
+      <c r="K41" s="107"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="34"/>
+      <c r="N41" s="34"/>
+      <c r="O41" s="34"/>
+      <c r="P41" s="34"/>
+      <c r="Q41" s="34"/>
+      <c r="R41" s="34"/>
+      <c r="S41" s="34"/>
+      <c r="T41" s="34"/>
+      <c r="U41" s="34"/>
+      <c r="V41" s="35"/>
     </row>
     <row r="42" spans="1:22" ht="23.1" customHeight="1">
       <c r="A42" s="23"/>
       <c r="B42" s="24"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="39"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="26"/>
       <c r="F42" s="19"/>
       <c r="G42" s="20"/>
       <c r="H42" s="19"/>
@@ -2535,25 +2535,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="37"/>
-      <c r="L42" s="25"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="26"/>
-      <c r="T42" s="26"/>
-      <c r="U42" s="26"/>
-      <c r="V42" s="27"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="34"/>
+      <c r="N42" s="34"/>
+      <c r="O42" s="34"/>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="34"/>
+      <c r="S42" s="34"/>
+      <c r="T42" s="34"/>
+      <c r="U42" s="34"/>
+      <c r="V42" s="35"/>
     </row>
     <row r="43" spans="1:22" ht="23.1" customHeight="1">
       <c r="A43" s="23"/>
       <c r="B43" s="24"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="39"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="26"/>
       <c r="F43" s="19"/>
       <c r="G43" s="20"/>
       <c r="H43" s="19"/>
@@ -2562,18 +2562,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="37"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="26"/>
-      <c r="T43" s="26"/>
-      <c r="U43" s="26"/>
-      <c r="V43" s="27"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="33"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="34"/>
+      <c r="S43" s="34"/>
+      <c r="T43" s="34"/>
+      <c r="U43" s="34"/>
+      <c r="V43" s="35"/>
     </row>
     <row r="44" spans="1:22" ht="23.1" customHeight="1">
       <c r="A44" s="23"/>
@@ -2589,18 +2589,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K44" s="37"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="26"/>
-      <c r="O44" s="26"/>
-      <c r="P44" s="26"/>
-      <c r="Q44" s="26"/>
-      <c r="R44" s="26"/>
-      <c r="S44" s="26"/>
-      <c r="T44" s="26"/>
-      <c r="U44" s="26"/>
-      <c r="V44" s="27"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="33"/>
+      <c r="M44" s="34"/>
+      <c r="N44" s="34"/>
+      <c r="O44" s="34"/>
+      <c r="P44" s="34"/>
+      <c r="Q44" s="34"/>
+      <c r="R44" s="34"/>
+      <c r="S44" s="34"/>
+      <c r="T44" s="34"/>
+      <c r="U44" s="34"/>
+      <c r="V44" s="35"/>
     </row>
     <row r="45" spans="1:22" ht="23.1" customHeight="1">
       <c r="A45" s="9"/>
@@ -2627,131 +2627,276 @@
       <c r="V45" s="9"/>
     </row>
     <row r="46" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="35"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="35"/>
-      <c r="M46" s="35"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="35"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="35"/>
-      <c r="V46" s="36"/>
+      <c r="B46" s="105"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="105"/>
+      <c r="K46" s="105"/>
+      <c r="L46" s="105"/>
+      <c r="M46" s="105"/>
+      <c r="N46" s="105"/>
+      <c r="O46" s="105"/>
+      <c r="P46" s="105"/>
+      <c r="Q46" s="105"/>
+      <c r="R46" s="105"/>
+      <c r="S46" s="105"/>
+      <c r="T46" s="105"/>
+      <c r="U46" s="105"/>
+      <c r="V46" s="106"/>
     </row>
     <row r="47" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A47" s="28"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="29"/>
-      <c r="T47" s="29"/>
-      <c r="U47" s="29"/>
-      <c r="V47" s="30"/>
+      <c r="A47" s="98"/>
+      <c r="B47" s="99"/>
+      <c r="C47" s="99"/>
+      <c r="D47" s="99"/>
+      <c r="E47" s="99"/>
+      <c r="F47" s="99"/>
+      <c r="G47" s="99"/>
+      <c r="H47" s="99"/>
+      <c r="I47" s="99"/>
+      <c r="J47" s="99"/>
+      <c r="K47" s="99"/>
+      <c r="L47" s="99"/>
+      <c r="M47" s="99"/>
+      <c r="N47" s="99"/>
+      <c r="O47" s="99"/>
+      <c r="P47" s="99"/>
+      <c r="Q47" s="99"/>
+      <c r="R47" s="99"/>
+      <c r="S47" s="99"/>
+      <c r="T47" s="99"/>
+      <c r="U47" s="99"/>
+      <c r="V47" s="100"/>
     </row>
     <row r="48" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A48" s="28"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="30"/>
+      <c r="A48" s="98"/>
+      <c r="B48" s="99"/>
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="99"/>
+      <c r="I48" s="99"/>
+      <c r="J48" s="99"/>
+      <c r="K48" s="99"/>
+      <c r="L48" s="99"/>
+      <c r="M48" s="99"/>
+      <c r="N48" s="99"/>
+      <c r="O48" s="99"/>
+      <c r="P48" s="99"/>
+      <c r="Q48" s="99"/>
+      <c r="R48" s="99"/>
+      <c r="S48" s="99"/>
+      <c r="T48" s="99"/>
+      <c r="U48" s="99"/>
+      <c r="V48" s="100"/>
     </row>
     <row r="49" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A49" s="31"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="32"/>
-      <c r="L49" s="32"/>
-      <c r="M49" s="32"/>
-      <c r="N49" s="32"/>
-      <c r="O49" s="32"/>
-      <c r="P49" s="32"/>
-      <c r="Q49" s="32"/>
-      <c r="R49" s="32"/>
-      <c r="S49" s="32"/>
-      <c r="T49" s="32"/>
-      <c r="U49" s="32"/>
-      <c r="V49" s="33"/>
+      <c r="A49" s="101"/>
+      <c r="B49" s="102"/>
+      <c r="C49" s="102"/>
+      <c r="D49" s="102"/>
+      <c r="E49" s="102"/>
+      <c r="F49" s="102"/>
+      <c r="G49" s="102"/>
+      <c r="H49" s="102"/>
+      <c r="I49" s="102"/>
+      <c r="J49" s="102"/>
+      <c r="K49" s="102"/>
+      <c r="L49" s="102"/>
+      <c r="M49" s="102"/>
+      <c r="N49" s="102"/>
+      <c r="O49" s="102"/>
+      <c r="P49" s="102"/>
+      <c r="Q49" s="102"/>
+      <c r="R49" s="102"/>
+      <c r="S49" s="102"/>
+      <c r="T49" s="102"/>
+      <c r="U49" s="102"/>
+      <c r="V49" s="103"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="219">
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="L39:V39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="A47:V49"/>
+    <mergeCell ref="A46:V46"/>
+    <mergeCell ref="L44:V44"/>
+    <mergeCell ref="L43:V43"/>
+    <mergeCell ref="L42:V42"/>
+    <mergeCell ref="L41:V41"/>
+    <mergeCell ref="L40:V40"/>
+    <mergeCell ref="L34:V34"/>
+    <mergeCell ref="L33:V33"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="L35:V35"/>
+    <mergeCell ref="L36:V36"/>
+    <mergeCell ref="L37:V37"/>
+    <mergeCell ref="L38:V38"/>
+    <mergeCell ref="L21:V21"/>
+    <mergeCell ref="L22:V22"/>
+    <mergeCell ref="L23:V23"/>
+    <mergeCell ref="L24:V24"/>
+    <mergeCell ref="L25:V25"/>
+    <mergeCell ref="L26:V26"/>
+    <mergeCell ref="L27:V27"/>
+    <mergeCell ref="L28:V28"/>
+    <mergeCell ref="L29:V29"/>
+    <mergeCell ref="L32:V32"/>
+    <mergeCell ref="L31:V31"/>
+    <mergeCell ref="L30:V30"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="Q1:R2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="R4:T5"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="O4:Q5"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="S1:V2"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L13:V13"/>
+    <mergeCell ref="L14:V14"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="J11:K12"/>
+    <mergeCell ref="L11:V12"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="A15:B15"/>
@@ -2776,176 +2921,31 @@
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="H17:I17"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L13:V13"/>
-    <mergeCell ref="L14:V14"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="J11:K12"/>
-    <mergeCell ref="L11:V12"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="Q1:R2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="R4:T5"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="O4:Q5"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="S1:V2"/>
-    <mergeCell ref="L35:V35"/>
-    <mergeCell ref="L36:V36"/>
-    <mergeCell ref="L37:V37"/>
-    <mergeCell ref="L38:V38"/>
-    <mergeCell ref="L21:V21"/>
-    <mergeCell ref="L22:V22"/>
-    <mergeCell ref="L23:V23"/>
-    <mergeCell ref="L24:V24"/>
-    <mergeCell ref="L25:V25"/>
-    <mergeCell ref="L26:V26"/>
-    <mergeCell ref="L27:V27"/>
-    <mergeCell ref="L28:V28"/>
-    <mergeCell ref="L29:V29"/>
-    <mergeCell ref="L32:V32"/>
-    <mergeCell ref="L31:V31"/>
-    <mergeCell ref="L30:V30"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A47:V49"/>
-    <mergeCell ref="A46:V46"/>
-    <mergeCell ref="L44:V44"/>
-    <mergeCell ref="L43:V43"/>
-    <mergeCell ref="L42:V42"/>
-    <mergeCell ref="L41:V41"/>
-    <mergeCell ref="L40:V40"/>
-    <mergeCell ref="L34:V34"/>
-    <mergeCell ref="L33:V33"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="L39:V39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="F26:G26"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:J2 E8:G9">

--- a/public/work-report-default-template.xlsx
+++ b/public/work-report-default-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\furugakihiromitsu\source\repos\WorkTimeManagementV2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D92179C-F5D4-4F55-BE38-57F841DDF9FA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03184DA3-8EF8-43AF-9E31-0D1E8705352C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,7 +282,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -714,11 +714,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -790,7 +803,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -798,6 +811,54 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -806,6 +867,21 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -815,6 +891,187 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -824,249 +1081,8 @@
     <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1130,10 +1146,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1446,54 +1458,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A1" s="74"/>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
+      <c r="A1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="77" t="s">
+      <c r="Q1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="78"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
     </row>
     <row r="2" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
-      <c r="V2" s="97"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+      <c r="V2" s="68"/>
     </row>
     <row r="3" spans="1:22" ht="23.1" customHeight="1">
       <c r="A3" s="6"/>
@@ -1520,64 +1532,64 @@
       <c r="V3" s="7"/>
     </row>
     <row r="4" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="80" t="s">
+      <c r="I4" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="81"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="90"/>
-      <c r="O4" s="91" t="s">
+      <c r="J4" s="52"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="61"/>
+      <c r="O4" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="84"/>
-      <c r="T4" s="85"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="56"/>
       <c r="U4" s="7"/>
       <c r="V4" s="17"/>
     </row>
     <row r="5" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="50"/>
       <c r="H5" s="12"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="95"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="87"/>
-      <c r="T5" s="88"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="58"/>
+      <c r="T5" s="59"/>
       <c r="U5" s="7"/>
       <c r="V5" s="16"/>
     </row>
     <row r="6" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="38"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
       <c r="H6" s="12"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -1593,15 +1605,15 @@
       <c r="V6" s="15"/>
     </row>
     <row r="7" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="32"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="107"/>
       <c r="H7" s="12"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -1618,28 +1630,28 @@
       <c r="V7" s="15"/>
     </row>
     <row r="8" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="62"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="93"/>
       <c r="H8" s="7"/>
       <c r="U8" s="7"/>
     </row>
     <row r="9" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="62"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="93"/>
       <c r="H9" s="7"/>
       <c r="O9" s="7"/>
       <c r="U9" s="7"/>
@@ -1670,134 +1682,134 @@
       <c r="V10" s="7"/>
     </row>
     <row r="11" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="49" t="s">
+      <c r="B11" s="94"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="49" t="s">
+      <c r="E11" s="81"/>
+      <c r="F11" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="50"/>
-      <c r="H11" s="49" t="s">
+      <c r="G11" s="81"/>
+      <c r="H11" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="50"/>
-      <c r="J11" s="53" t="s">
+      <c r="I11" s="81"/>
+      <c r="J11" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="54"/>
-      <c r="L11" s="53" t="s">
+      <c r="K11" s="85"/>
+      <c r="L11" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="57"/>
-      <c r="N11" s="57"/>
-      <c r="O11" s="57"/>
-      <c r="P11" s="57"/>
-      <c r="Q11" s="57"/>
-      <c r="R11" s="57"/>
-      <c r="S11" s="57"/>
-      <c r="T11" s="57"/>
-      <c r="U11" s="57"/>
-      <c r="V11" s="54"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="88"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="88"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="85"/>
     </row>
     <row r="12" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="58"/>
-      <c r="S12" s="58"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="58"/>
-      <c r="V12" s="56"/>
+      <c r="A12" s="96"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="87"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="89"/>
+      <c r="O12" s="89"/>
+      <c r="P12" s="89"/>
+      <c r="Q12" s="89"/>
+      <c r="R12" s="89"/>
+      <c r="S12" s="89"/>
+      <c r="T12" s="89"/>
+      <c r="U12" s="89"/>
+      <c r="V12" s="87"/>
     </row>
     <row r="13" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70">
+      <c r="B13" s="100"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="101">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E13" s="71"/>
-      <c r="F13" s="70">
+      <c r="E13" s="102"/>
+      <c r="F13" s="101">
         <v>0.79166666666666663</v>
       </c>
-      <c r="G13" s="71"/>
-      <c r="H13" s="72">
+      <c r="G13" s="102"/>
+      <c r="H13" s="103">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I13" s="73"/>
-      <c r="J13" s="70">
+      <c r="I13" s="104"/>
+      <c r="J13" s="101">
         <v>0.33333333333333331</v>
       </c>
-      <c r="K13" s="71"/>
-      <c r="L13" s="43" t="s">
+      <c r="K13" s="102"/>
+      <c r="L13" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="44"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
-      <c r="P13" s="44"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
-      <c r="U13" s="44"/>
-      <c r="V13" s="45"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="75"/>
+      <c r="Q13" s="75"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="75"/>
+      <c r="V13" s="76"/>
     </row>
     <row r="14" spans="1:22" ht="23.1" customHeight="1">
       <c r="A14" s="23"/>
       <c r="B14" s="24"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
       <c r="F14" s="19"/>
       <c r="G14" s="20"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41" t="str">
+      <c r="H14" s="70"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72" t="str">
         <f t="shared" ref="J14" si="0">IF(D14="","",(ABS(F14-D14))-H14)</f>
         <v/>
       </c>
-      <c r="K14" s="42"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="48"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="77"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="78"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="78"/>
+      <c r="U14" s="78"/>
+      <c r="V14" s="79"/>
     </row>
     <row r="15" spans="1:22" ht="23.1" customHeight="1">
       <c r="A15" s="23"/>
       <c r="B15" s="24"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="26"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="39"/>
       <c r="F15" s="19"/>
       <c r="G15" s="20"/>
       <c r="H15" s="19"/>
@@ -1806,25 +1818,25 @@
         <f t="shared" ref="J15:J44" si="1">IF(D15="","",(ABS(F15-D15))-H15)</f>
         <v/>
       </c>
-      <c r="K15" s="22"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="35"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="27"/>
     </row>
     <row r="16" spans="1:22" ht="23.1" customHeight="1">
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="26"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="39"/>
       <c r="F16" s="19"/>
       <c r="G16" s="20"/>
       <c r="H16" s="19"/>
@@ -1833,79 +1845,79 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K16" s="22"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="35"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="27"/>
     </row>
     <row r="17" spans="1:22" ht="23.1" customHeight="1">
       <c r="A17" s="23"/>
       <c r="B17" s="24"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="26"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
       <c r="H17" s="19"/>
       <c r="I17" s="20"/>
       <c r="J17" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="22"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="35"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="26"/>
+      <c r="U17" s="26"/>
+      <c r="V17" s="27"/>
     </row>
     <row r="18" spans="1:22" ht="23.1" customHeight="1">
       <c r="A18" s="23"/>
       <c r="B18" s="24"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="26"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="19"/>
       <c r="I18" s="20"/>
       <c r="J18" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="22"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="35"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="26"/>
+      <c r="U18" s="26"/>
+      <c r="V18" s="27"/>
     </row>
     <row r="19" spans="1:22" ht="23.1" customHeight="1">
       <c r="A19" s="23"/>
       <c r="B19" s="24"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="39"/>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
       <c r="H19" s="19"/>
@@ -1914,25 +1926,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="22"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="35"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="26"/>
+      <c r="U19" s="26"/>
+      <c r="V19" s="27"/>
     </row>
     <row r="20" spans="1:22" ht="23.1" customHeight="1">
       <c r="A20" s="23"/>
       <c r="B20" s="24"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="26"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="39"/>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="19"/>
@@ -1941,25 +1953,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="22"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="35"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="26"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="26"/>
+      <c r="V20" s="27"/>
     </row>
     <row r="21" spans="1:22" ht="23.1" customHeight="1">
       <c r="A21" s="23"/>
       <c r="B21" s="24"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="26"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="39"/>
       <c r="F21" s="19"/>
       <c r="G21" s="20"/>
       <c r="H21" s="19"/>
@@ -1968,25 +1980,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="22"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="34"/>
-      <c r="V21" s="35"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
+      <c r="S21" s="26"/>
+      <c r="T21" s="26"/>
+      <c r="U21" s="26"/>
+      <c r="V21" s="27"/>
     </row>
     <row r="22" spans="1:22" ht="23.1" customHeight="1">
       <c r="A22" s="23"/>
       <c r="B22" s="24"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="39"/>
       <c r="F22" s="19"/>
       <c r="G22" s="20"/>
       <c r="H22" s="19"/>
@@ -1995,25 +2007,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="22"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="34"/>
-      <c r="V22" s="35"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="27"/>
     </row>
     <row r="23" spans="1:22" ht="23.1" customHeight="1">
       <c r="A23" s="23"/>
       <c r="B23" s="24"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="26"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="39"/>
       <c r="F23" s="19"/>
       <c r="G23" s="20"/>
       <c r="H23" s="19"/>
@@ -2022,18 +2034,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="22"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="34"/>
-      <c r="V23" s="35"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="26"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="26"/>
+      <c r="V23" s="27"/>
     </row>
     <row r="24" spans="1:22" ht="23.1" customHeight="1">
       <c r="A24" s="23"/>
@@ -2049,18 +2061,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="22"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
-      <c r="O24" s="34"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34"/>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="34"/>
-      <c r="V24" s="35"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="26"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="26"/>
+      <c r="V24" s="27"/>
     </row>
     <row r="25" spans="1:22" ht="23.1" customHeight="1">
       <c r="A25" s="23"/>
@@ -2076,25 +2088,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="22"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
-      <c r="O25" s="34"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="35"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="26"/>
+      <c r="U25" s="26"/>
+      <c r="V25" s="27"/>
     </row>
     <row r="26" spans="1:22" ht="23.1" customHeight="1">
       <c r="A26" s="23"/>
       <c r="B26" s="24"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="26"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="39"/>
       <c r="F26" s="19"/>
       <c r="G26" s="20"/>
       <c r="H26" s="19"/>
@@ -2103,25 +2115,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="22"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
-      <c r="S26" s="34"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="34"/>
-      <c r="V26" s="35"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="27"/>
     </row>
     <row r="27" spans="1:22" ht="23.1" customHeight="1">
       <c r="A27" s="23"/>
       <c r="B27" s="24"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="26"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="39"/>
       <c r="F27" s="19"/>
       <c r="G27" s="20"/>
       <c r="H27" s="19"/>
@@ -2130,25 +2142,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="22"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="34"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="34"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="35"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="27"/>
     </row>
     <row r="28" spans="1:22" ht="23.1" customHeight="1">
       <c r="A28" s="23"/>
       <c r="B28" s="24"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="26"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="39"/>
       <c r="F28" s="19"/>
       <c r="G28" s="20"/>
       <c r="H28" s="19"/>
@@ -2157,25 +2169,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="34"/>
-      <c r="V28" s="35"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="27"/>
     </row>
     <row r="29" spans="1:22" ht="23.1" customHeight="1">
       <c r="A29" s="23"/>
       <c r="B29" s="24"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="26"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="39"/>
       <c r="F29" s="19"/>
       <c r="G29" s="20"/>
       <c r="H29" s="19"/>
@@ -2184,25 +2196,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="22"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="34"/>
-      <c r="R29" s="34"/>
-      <c r="S29" s="34"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="35"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="26"/>
+      <c r="T29" s="26"/>
+      <c r="U29" s="26"/>
+      <c r="V29" s="27"/>
     </row>
     <row r="30" spans="1:22" ht="23.1" customHeight="1">
       <c r="A30" s="23"/>
       <c r="B30" s="24"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="26"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="39"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="19"/>
@@ -2211,18 +2223,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="22"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="34"/>
-      <c r="V30" s="35"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="27"/>
     </row>
     <row r="31" spans="1:22" ht="23.1" customHeight="1">
       <c r="A31" s="23"/>
@@ -2238,18 +2250,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="22"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="35"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26"/>
+      <c r="V31" s="27"/>
     </row>
     <row r="32" spans="1:22" ht="23.1" customHeight="1">
       <c r="A32" s="23"/>
@@ -2265,18 +2277,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="22"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="34"/>
-      <c r="V32" s="35"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="27"/>
     </row>
     <row r="33" spans="1:22" ht="23.1" customHeight="1">
       <c r="A33" s="23"/>
@@ -2292,25 +2304,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="22"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="34"/>
-      <c r="V33" s="35"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="26"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="27"/>
     </row>
     <row r="34" spans="1:22" ht="23.1" customHeight="1">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="26"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="39"/>
       <c r="F34" s="19"/>
       <c r="G34" s="20"/>
       <c r="H34" s="19"/>
@@ -2319,25 +2331,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="22"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="35"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="26"/>
+      <c r="T34" s="26"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="27"/>
     </row>
     <row r="35" spans="1:22" ht="23.1" customHeight="1">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="26"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="39"/>
       <c r="F35" s="19"/>
       <c r="G35" s="20"/>
       <c r="H35" s="19"/>
@@ -2346,25 +2358,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="34"/>
-      <c r="V35" s="35"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="26"/>
+      <c r="S35" s="26"/>
+      <c r="T35" s="26"/>
+      <c r="U35" s="26"/>
+      <c r="V35" s="27"/>
     </row>
     <row r="36" spans="1:22" ht="23.1" customHeight="1">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="26"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="39"/>
       <c r="F36" s="19"/>
       <c r="G36" s="20"/>
       <c r="H36" s="19"/>
@@ -2373,25 +2385,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="22"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="35"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="26"/>
+      <c r="U36" s="26"/>
+      <c r="V36" s="27"/>
     </row>
     <row r="37" spans="1:22" ht="23.1" customHeight="1">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="26"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="39"/>
       <c r="F37" s="19"/>
       <c r="G37" s="20"/>
       <c r="H37" s="19"/>
@@ -2400,18 +2412,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="22"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="34"/>
-      <c r="V37" s="35"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="26"/>
+      <c r="S37" s="26"/>
+      <c r="T37" s="26"/>
+      <c r="U37" s="26"/>
+      <c r="V37" s="27"/>
     </row>
     <row r="38" spans="1:22" ht="23.1" customHeight="1">
       <c r="A38" s="23"/>
@@ -2427,18 +2439,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="22"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="S38" s="34"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="34"/>
-      <c r="V38" s="35"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
+      <c r="S38" s="26"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="26"/>
+      <c r="V38" s="27"/>
     </row>
     <row r="39" spans="1:22" ht="23.1" customHeight="1">
       <c r="A39" s="23"/>
@@ -2454,18 +2466,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="107"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="35"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="26"/>
+      <c r="S39" s="26"/>
+      <c r="T39" s="26"/>
+      <c r="U39" s="26"/>
+      <c r="V39" s="27"/>
     </row>
     <row r="40" spans="1:22" ht="23.1" customHeight="1">
       <c r="A40" s="23"/>
@@ -2481,18 +2493,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="107"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="34"/>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="34"/>
-      <c r="V40" s="35"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+      <c r="P40" s="26"/>
+      <c r="Q40" s="26"/>
+      <c r="R40" s="26"/>
+      <c r="S40" s="26"/>
+      <c r="T40" s="26"/>
+      <c r="U40" s="26"/>
+      <c r="V40" s="27"/>
     </row>
     <row r="41" spans="1:22" ht="23.1" customHeight="1">
       <c r="A41" s="23"/>
@@ -2508,25 +2520,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="107"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="34"/>
-      <c r="N41" s="34"/>
-      <c r="O41" s="34"/>
-      <c r="P41" s="34"/>
-      <c r="Q41" s="34"/>
-      <c r="R41" s="34"/>
-      <c r="S41" s="34"/>
-      <c r="T41" s="34"/>
-      <c r="U41" s="34"/>
-      <c r="V41" s="35"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="25"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="26"/>
+      <c r="S41" s="26"/>
+      <c r="T41" s="26"/>
+      <c r="U41" s="26"/>
+      <c r="V41" s="27"/>
     </row>
     <row r="42" spans="1:22" ht="23.1" customHeight="1">
       <c r="A42" s="23"/>
       <c r="B42" s="24"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="26"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="39"/>
       <c r="F42" s="19"/>
       <c r="G42" s="20"/>
       <c r="H42" s="19"/>
@@ -2535,25 +2547,25 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="22"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="34"/>
-      <c r="N42" s="34"/>
-      <c r="O42" s="34"/>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="34"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="34"/>
-      <c r="U42" s="34"/>
-      <c r="V42" s="35"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="26"/>
+      <c r="T42" s="26"/>
+      <c r="U42" s="26"/>
+      <c r="V42" s="27"/>
     </row>
     <row r="43" spans="1:22" ht="23.1" customHeight="1">
       <c r="A43" s="23"/>
       <c r="B43" s="24"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="26"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="39"/>
       <c r="F43" s="19"/>
       <c r="G43" s="20"/>
       <c r="H43" s="19"/>
@@ -2562,18 +2574,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="22"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="34"/>
-      <c r="N43" s="34"/>
-      <c r="O43" s="34"/>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="34"/>
-      <c r="R43" s="34"/>
-      <c r="S43" s="34"/>
-      <c r="T43" s="34"/>
-      <c r="U43" s="34"/>
-      <c r="V43" s="35"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="25"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="26"/>
+      <c r="S43" s="26"/>
+      <c r="T43" s="26"/>
+      <c r="U43" s="26"/>
+      <c r="V43" s="27"/>
     </row>
     <row r="44" spans="1:22" ht="23.1" customHeight="1">
       <c r="A44" s="23"/>
@@ -2589,18 +2601,18 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K44" s="22"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="34"/>
-      <c r="N44" s="34"/>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-      <c r="U44" s="34"/>
-      <c r="V44" s="35"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="26"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="26"/>
+      <c r="S44" s="26"/>
+      <c r="T44" s="26"/>
+      <c r="U44" s="26"/>
+      <c r="V44" s="27"/>
     </row>
     <row r="45" spans="1:22" ht="23.1" customHeight="1">
       <c r="A45" s="9"/>
@@ -2627,122 +2639,285 @@
       <c r="V45" s="9"/>
     </row>
     <row r="46" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A46" s="104" t="s">
+      <c r="A46" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="105"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="105"/>
-      <c r="I46" s="105"/>
-      <c r="J46" s="105"/>
-      <c r="K46" s="105"/>
-      <c r="L46" s="105"/>
-      <c r="M46" s="105"/>
-      <c r="N46" s="105"/>
-      <c r="O46" s="105"/>
-      <c r="P46" s="105"/>
-      <c r="Q46" s="105"/>
-      <c r="R46" s="105"/>
-      <c r="S46" s="105"/>
-      <c r="T46" s="105"/>
-      <c r="U46" s="105"/>
-      <c r="V46" s="106"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="35"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="35"/>
+      <c r="V46" s="36"/>
     </row>
     <row r="47" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A47" s="98"/>
-      <c r="B47" s="99"/>
-      <c r="C47" s="99"/>
-      <c r="D47" s="99"/>
-      <c r="E47" s="99"/>
-      <c r="F47" s="99"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="99"/>
-      <c r="I47" s="99"/>
-      <c r="J47" s="99"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="99"/>
-      <c r="N47" s="99"/>
-      <c r="O47" s="99"/>
-      <c r="P47" s="99"/>
-      <c r="Q47" s="99"/>
-      <c r="R47" s="99"/>
-      <c r="S47" s="99"/>
-      <c r="T47" s="99"/>
-      <c r="U47" s="99"/>
-      <c r="V47" s="100"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+      <c r="T47" s="29"/>
+      <c r="U47" s="29"/>
+      <c r="V47" s="30"/>
     </row>
     <row r="48" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A48" s="98"/>
-      <c r="B48" s="99"/>
-      <c r="C48" s="99"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
-      <c r="H48" s="99"/>
-      <c r="I48" s="99"/>
-      <c r="J48" s="99"/>
-      <c r="K48" s="99"/>
-      <c r="L48" s="99"/>
-      <c r="M48" s="99"/>
-      <c r="N48" s="99"/>
-      <c r="O48" s="99"/>
-      <c r="P48" s="99"/>
-      <c r="Q48" s="99"/>
-      <c r="R48" s="99"/>
-      <c r="S48" s="99"/>
-      <c r="T48" s="99"/>
-      <c r="U48" s="99"/>
-      <c r="V48" s="100"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="29"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="30"/>
     </row>
     <row r="49" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A49" s="101"/>
-      <c r="B49" s="102"/>
-      <c r="C49" s="102"/>
-      <c r="D49" s="102"/>
-      <c r="E49" s="102"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="102"/>
-      <c r="H49" s="102"/>
-      <c r="I49" s="102"/>
-      <c r="J49" s="102"/>
-      <c r="K49" s="102"/>
-      <c r="L49" s="102"/>
-      <c r="M49" s="102"/>
-      <c r="N49" s="102"/>
-      <c r="O49" s="102"/>
-      <c r="P49" s="102"/>
-      <c r="Q49" s="102"/>
-      <c r="R49" s="102"/>
-      <c r="S49" s="102"/>
-      <c r="T49" s="102"/>
-      <c r="U49" s="102"/>
-      <c r="V49" s="103"/>
+      <c r="A49" s="31"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="33"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="219">
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="L39:V39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L20:V20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="L19:V19"/>
+    <mergeCell ref="L18:V18"/>
+    <mergeCell ref="L17:V17"/>
+    <mergeCell ref="L16:V16"/>
+    <mergeCell ref="L15:V15"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L13:V13"/>
+    <mergeCell ref="L14:V14"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="J11:K12"/>
+    <mergeCell ref="L11:V12"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="Q1:R2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="R4:T5"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="O4:Q5"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="S1:V2"/>
+    <mergeCell ref="L35:V35"/>
+    <mergeCell ref="L36:V36"/>
+    <mergeCell ref="L37:V37"/>
+    <mergeCell ref="L38:V38"/>
+    <mergeCell ref="L21:V21"/>
+    <mergeCell ref="L22:V22"/>
+    <mergeCell ref="L23:V23"/>
+    <mergeCell ref="L24:V24"/>
+    <mergeCell ref="L25:V25"/>
+    <mergeCell ref="L26:V26"/>
+    <mergeCell ref="L27:V27"/>
+    <mergeCell ref="L28:V28"/>
+    <mergeCell ref="L29:V29"/>
+    <mergeCell ref="L32:V32"/>
+    <mergeCell ref="L31:V31"/>
+    <mergeCell ref="L30:V30"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="A47:V49"/>
     <mergeCell ref="A46:V46"/>
     <mergeCell ref="L44:V44"/>
@@ -2767,185 +2942,22 @@
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="H43:I43"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="L35:V35"/>
-    <mergeCell ref="L36:V36"/>
-    <mergeCell ref="L37:V37"/>
-    <mergeCell ref="L38:V38"/>
-    <mergeCell ref="L21:V21"/>
-    <mergeCell ref="L22:V22"/>
-    <mergeCell ref="L23:V23"/>
-    <mergeCell ref="L24:V24"/>
-    <mergeCell ref="L25:V25"/>
-    <mergeCell ref="L26:V26"/>
-    <mergeCell ref="L27:V27"/>
-    <mergeCell ref="L28:V28"/>
-    <mergeCell ref="L29:V29"/>
-    <mergeCell ref="L32:V32"/>
-    <mergeCell ref="L31:V31"/>
-    <mergeCell ref="L30:V30"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="Q1:R2"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="R4:T5"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="O4:Q5"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="S1:V2"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L13:V13"/>
-    <mergeCell ref="L14:V14"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="J11:K12"/>
-    <mergeCell ref="L11:V12"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L20:V20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="L19:V19"/>
-    <mergeCell ref="L18:V18"/>
-    <mergeCell ref="L17:V17"/>
-    <mergeCell ref="L16:V16"/>
-    <mergeCell ref="L15:V15"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="L39:V39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J39:K39"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:J2 E8:G9">

--- a/public/work-report-default-template.xlsx
+++ b/public/work-report-default-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\furugakihiromitsu\source\repos\WorkTimeManagementV2\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03184DA3-8EF8-43AF-9E31-0D1E8705352C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{4B95D6CF-63C2-4448-9CBC-42EDA699692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7081D71C-13BE-4204-AF17-3DBFA06189E0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,7 @@
     <numFmt numFmtId="179" formatCode="h:mm;@"/>
     <numFmt numFmtId="180" formatCode="0.0&quot;日&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -255,6 +255,13 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -282,7 +289,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -714,24 +721,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -789,6 +786,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1081,11 +1084,9 @@
     <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="パーセント" xfId="1" builtinId="5"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
@@ -1146,6 +1147,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1450,64 +1455,64 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V49"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
+  <dimension ref="A1:AA49"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="22" width="5.125" style="3" customWidth="1"/>
     <col min="23" max="16384" width="12.625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A1" s="40"/>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
+    <row r="1" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
       <c r="K1" s="1"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="43" t="s">
+      <c r="Q1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="44"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-    </row>
-    <row r="2" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
+    </row>
+    <row r="2" spans="1:27" ht="23.1" customHeight="1" thickBot="1">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="68"/>
-    </row>
-    <row r="3" spans="1:22" ht="23.1" customHeight="1">
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70"/>
+      <c r="V2" s="70"/>
+    </row>
+    <row r="3" spans="1:27" ht="23.1" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1531,65 +1536,65 @@
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
     </row>
-    <row r="4" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A4" s="46" t="s">
+    <row r="4" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A4" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="52"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="61"/>
-      <c r="O4" s="62" t="s">
+      <c r="J4" s="54"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="63"/>
+      <c r="O4" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="56"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="57"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="7"/>
       <c r="V4" s="17"/>
     </row>
-    <row r="5" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A5" s="46" t="s">
+    <row r="5" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A5" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="50"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="52"/>
       <c r="H5" s="12"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="57"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="59"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="60"/>
+      <c r="T5" s="61"/>
       <c r="U5" s="7"/>
       <c r="V5" s="16"/>
     </row>
-    <row r="6" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A6" s="46" t="s">
+    <row r="6" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A6" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="52"/>
       <c r="H6" s="12"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -1604,16 +1609,16 @@
       <c r="U6" s="7"/>
       <c r="V6" s="15"/>
     </row>
-    <row r="7" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A7" s="46" t="s">
+    <row r="7" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A7" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="107"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="109"/>
       <c r="H7" s="12"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -1627,37 +1632,36 @@
       <c r="S7" s="13"/>
       <c r="T7" s="13"/>
       <c r="U7" s="7"/>
-      <c r="V7" s="15"/>
-    </row>
-    <row r="8" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A8" s="90" t="s">
+    </row>
+    <row r="8" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A8" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="93"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="95"/>
       <c r="H8" s="7"/>
       <c r="U8" s="7"/>
     </row>
-    <row r="9" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
-      <c r="A9" s="90" t="s">
+    <row r="9" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A9" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="93"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="95"/>
       <c r="H9" s="7"/>
       <c r="O9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
     </row>
-    <row r="10" spans="1:22" ht="23.1" customHeight="1" outlineLevel="1">
+    <row r="10" spans="1:27" ht="23.1" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1681,938 +1685,941 @@
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
     </row>
-    <row r="11" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A11" s="80" t="s">
+    <row r="11" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A11" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="94"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="80" t="s">
+      <c r="B11" s="96"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="80" t="s">
+      <c r="E11" s="83"/>
+      <c r="F11" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="81"/>
-      <c r="H11" s="80" t="s">
+      <c r="G11" s="83"/>
+      <c r="H11" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="81"/>
-      <c r="J11" s="84" t="s">
+      <c r="I11" s="83"/>
+      <c r="J11" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="85"/>
-      <c r="L11" s="84" t="s">
+      <c r="K11" s="87"/>
+      <c r="L11" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="M11" s="88"/>
-      <c r="N11" s="88"/>
-      <c r="O11" s="88"/>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="85"/>
-    </row>
-    <row r="12" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A12" s="96"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="87"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="89"/>
-      <c r="N12" s="89"/>
-      <c r="O12" s="89"/>
-      <c r="P12" s="89"/>
-      <c r="Q12" s="89"/>
-      <c r="R12" s="89"/>
-      <c r="S12" s="89"/>
-      <c r="T12" s="89"/>
-      <c r="U12" s="89"/>
-      <c r="V12" s="87"/>
-    </row>
-    <row r="13" spans="1:22" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A13" s="99" t="s">
+      <c r="M11" s="90"/>
+      <c r="N11" s="90"/>
+      <c r="O11" s="90"/>
+      <c r="P11" s="90"/>
+      <c r="Q11" s="90"/>
+      <c r="R11" s="90"/>
+      <c r="S11" s="90"/>
+      <c r="T11" s="90"/>
+      <c r="U11" s="90"/>
+      <c r="V11" s="87"/>
+    </row>
+    <row r="12" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="89"/>
+      <c r="L12" s="88"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="91"/>
+      <c r="R12" s="91"/>
+      <c r="S12" s="91"/>
+      <c r="T12" s="91"/>
+      <c r="U12" s="91"/>
+      <c r="V12" s="89"/>
+    </row>
+    <row r="13" spans="1:27" ht="23.1" customHeight="1" thickBot="1">
+      <c r="A13" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="100"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="101">
+      <c r="B13" s="102"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="103">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="101">
+      <c r="E13" s="104"/>
+      <c r="F13" s="103">
         <v>0.79166666666666663</v>
       </c>
-      <c r="G13" s="102"/>
-      <c r="H13" s="103">
+      <c r="G13" s="104"/>
+      <c r="H13" s="105">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="I13" s="104"/>
-      <c r="J13" s="101">
+      <c r="I13" s="106"/>
+      <c r="J13" s="103">
         <v>0.33333333333333331</v>
       </c>
-      <c r="K13" s="102"/>
-      <c r="L13" s="74" t="s">
+      <c r="K13" s="104"/>
+      <c r="L13" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="75"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="75"/>
-      <c r="V13" s="76"/>
-    </row>
-    <row r="14" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24"/>
+      <c r="M13" s="77"/>
+      <c r="N13" s="77"/>
+      <c r="O13" s="77"/>
+      <c r="P13" s="77"/>
+      <c r="Q13" s="77"/>
+      <c r="R13" s="77"/>
+      <c r="S13" s="77"/>
+      <c r="T13" s="77"/>
+      <c r="U13" s="77"/>
+      <c r="V13" s="78"/>
+    </row>
+    <row r="14" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="72" t="str">
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="74" t="str">
         <f t="shared" ref="J14" si="0">IF(D14="","",(ABS(F14-D14))-H14)</f>
         <v/>
       </c>
-      <c r="K14" s="73"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="78"/>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="78"/>
-      <c r="U14" s="78"/>
-      <c r="V14" s="79"/>
-    </row>
-    <row r="15" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="80"/>
+      <c r="R14" s="80"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="80"/>
+      <c r="U14" s="80"/>
+      <c r="V14" s="81"/>
+    </row>
+    <row r="15" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="21" t="str">
+      <c r="D15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23" t="str">
         <f t="shared" ref="J15:J44" si="1">IF(D15="","",(ABS(F15-D15))-H15)</f>
         <v/>
       </c>
-      <c r="K15" s="37"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
-      <c r="V15" s="27"/>
-    </row>
-    <row r="16" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="29"/>
+    </row>
+    <row r="16" spans="1:27" ht="23.1" customHeight="1">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21" t="str">
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K16" s="37"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
-      <c r="R16" s="26"/>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="27"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="29"/>
+      <c r="X16" s="19"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="19"/>
     </row>
     <row r="17" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="21" t="str">
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K17" s="37"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="26"/>
-      <c r="S17" s="26"/>
-      <c r="T17" s="26"/>
-      <c r="U17" s="26"/>
-      <c r="V17" s="27"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="28"/>
+      <c r="V17" s="29"/>
     </row>
     <row r="18" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="21" t="str">
+      <c r="D18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K18" s="37"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-      <c r="V18" s="27"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
+      <c r="V18" s="29"/>
     </row>
     <row r="19" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21" t="str">
+      <c r="D19" s="40"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K19" s="37"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-      <c r="V19" s="27"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="29"/>
     </row>
     <row r="20" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="21" t="str">
+      <c r="D20" s="40"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K20" s="37"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-      <c r="V20" s="27"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="29"/>
     </row>
     <row r="21" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="21" t="str">
+      <c r="D21" s="40"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K21" s="37"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="27"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="28"/>
+      <c r="V21" s="29"/>
     </row>
     <row r="22" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21" t="str">
+      <c r="D22" s="40"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K22" s="37"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="26"/>
-      <c r="Q22" s="26"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-      <c r="V22" s="27"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="29"/>
     </row>
     <row r="23" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="26"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="21" t="str">
+      <c r="D23" s="40"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K23" s="37"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="26"/>
-      <c r="Q23" s="26"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="27"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="29"/>
     </row>
     <row r="24" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="26"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="21" t="str">
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K24" s="37"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="27"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
+      <c r="V24" s="29"/>
     </row>
     <row r="25" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="26"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="21" t="str">
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K25" s="37"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="26"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="26"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
-      <c r="V25" s="27"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="29"/>
     </row>
     <row r="26" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="26"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="21" t="str">
+      <c r="D26" s="40"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K26" s="37"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="26"/>
-      <c r="Q26" s="26"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="27"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="29"/>
     </row>
     <row r="27" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A27" s="23"/>
-      <c r="B27" s="24"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="21" t="str">
+      <c r="D27" s="40"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K27" s="37"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="27"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="29"/>
     </row>
     <row r="28" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A28" s="23"/>
-      <c r="B28" s="24"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="26"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="21" t="str">
+      <c r="D28" s="40"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="37"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="27"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="29"/>
     </row>
     <row r="29" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A29" s="23"/>
-      <c r="B29" s="24"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="26"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="21" t="str">
+      <c r="D29" s="40"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K29" s="37"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="27"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="29"/>
     </row>
     <row r="30" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A30" s="23"/>
-      <c r="B30" s="24"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="21" t="str">
+      <c r="D30" s="40"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K30" s="37"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="27"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="28"/>
+      <c r="V30" s="29"/>
     </row>
     <row r="31" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A31" s="23"/>
-      <c r="B31" s="24"/>
+      <c r="A31" s="25"/>
+      <c r="B31" s="26"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="21" t="str">
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K31" s="37"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="27"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="28"/>
+      <c r="V31" s="29"/>
     </row>
     <row r="32" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A32" s="23"/>
-      <c r="B32" s="24"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="21" t="str">
+      <c r="D32" s="21"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="37"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="27"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="29"/>
     </row>
     <row r="33" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A33" s="23"/>
-      <c r="B33" s="24"/>
+      <c r="A33" s="25"/>
+      <c r="B33" s="26"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="21" t="str">
+      <c r="D33" s="21"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="37"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="27"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="28"/>
+      <c r="V33" s="29"/>
     </row>
     <row r="34" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A34" s="23"/>
-      <c r="B34" s="24"/>
+      <c r="A34" s="25"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="21" t="str">
+      <c r="D34" s="40"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K34" s="37"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="27"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="29"/>
     </row>
     <row r="35" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A35" s="23"/>
-      <c r="B35" s="24"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="26"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="21" t="str">
+      <c r="D35" s="40"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K35" s="37"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="26"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="26"/>
-      <c r="V35" s="27"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="29"/>
     </row>
     <row r="36" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A36" s="23"/>
-      <c r="B36" s="24"/>
+      <c r="A36" s="25"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="8"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="21" t="str">
+      <c r="D36" s="40"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="37"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="26"/>
-      <c r="V36" s="27"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
+      <c r="V36" s="29"/>
     </row>
     <row r="37" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A37" s="23"/>
-      <c r="B37" s="24"/>
+      <c r="A37" s="25"/>
+      <c r="B37" s="26"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="21" t="str">
+      <c r="D37" s="40"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K37" s="37"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="26"/>
-      <c r="V37" s="27"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="29"/>
     </row>
     <row r="38" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A38" s="23"/>
-      <c r="B38" s="24"/>
+      <c r="A38" s="25"/>
+      <c r="B38" s="26"/>
       <c r="C38" s="8"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="21" t="str">
+      <c r="D38" s="21"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K38" s="37"/>
-      <c r="L38" s="25"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="27"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
+      <c r="V38" s="29"/>
     </row>
     <row r="39" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A39" s="23"/>
-      <c r="B39" s="24"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="26"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="21" t="str">
+      <c r="D39" s="21"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K39" s="22"/>
-      <c r="L39" s="25"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="26"/>
-      <c r="O39" s="26"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26"/>
-      <c r="S39" s="26"/>
-      <c r="T39" s="26"/>
-      <c r="U39" s="26"/>
-      <c r="V39" s="27"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="29"/>
     </row>
     <row r="40" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A40" s="23"/>
-      <c r="B40" s="24"/>
+      <c r="A40" s="25"/>
+      <c r="B40" s="26"/>
       <c r="C40" s="8"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="21" t="str">
+      <c r="D40" s="21"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="25"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="26"/>
-      <c r="Q40" s="26"/>
-      <c r="R40" s="26"/>
-      <c r="S40" s="26"/>
-      <c r="T40" s="26"/>
-      <c r="U40" s="26"/>
-      <c r="V40" s="27"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="29"/>
     </row>
     <row r="41" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A41" s="23"/>
-      <c r="B41" s="24"/>
+      <c r="A41" s="25"/>
+      <c r="B41" s="26"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="21" t="str">
+      <c r="D41" s="21"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K41" s="22"/>
-      <c r="L41" s="25"/>
-      <c r="M41" s="26"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="26"/>
-      <c r="P41" s="26"/>
-      <c r="Q41" s="26"/>
-      <c r="R41" s="26"/>
-      <c r="S41" s="26"/>
-      <c r="T41" s="26"/>
-      <c r="U41" s="26"/>
-      <c r="V41" s="27"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+      <c r="R41" s="28"/>
+      <c r="S41" s="28"/>
+      <c r="T41" s="28"/>
+      <c r="U41" s="28"/>
+      <c r="V41" s="29"/>
     </row>
     <row r="42" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A42" s="23"/>
-      <c r="B42" s="24"/>
+      <c r="A42" s="25"/>
+      <c r="B42" s="26"/>
       <c r="C42" s="8"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="21" t="str">
+      <c r="D42" s="40"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K42" s="37"/>
-      <c r="L42" s="25"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="26"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="26"/>
-      <c r="T42" s="26"/>
-      <c r="U42" s="26"/>
-      <c r="V42" s="27"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
+      <c r="V42" s="29"/>
     </row>
     <row r="43" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A43" s="23"/>
-      <c r="B43" s="24"/>
+      <c r="A43" s="25"/>
+      <c r="B43" s="26"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="21" t="str">
+      <c r="D43" s="40"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K43" s="37"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="26"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="26"/>
-      <c r="T43" s="26"/>
-      <c r="U43" s="26"/>
-      <c r="V43" s="27"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="27"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="29"/>
     </row>
     <row r="44" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A44" s="23"/>
-      <c r="B44" s="24"/>
+      <c r="A44" s="25"/>
+      <c r="B44" s="26"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="21" t="str">
+      <c r="D44" s="21"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K44" s="37"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="26"/>
-      <c r="O44" s="26"/>
-      <c r="P44" s="26"/>
-      <c r="Q44" s="26"/>
-      <c r="R44" s="26"/>
-      <c r="S44" s="26"/>
-      <c r="T44" s="26"/>
-      <c r="U44" s="26"/>
-      <c r="V44" s="27"/>
+      <c r="K44" s="39"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="28"/>
+      <c r="O44" s="28"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="28"/>
+      <c r="R44" s="28"/>
+      <c r="S44" s="28"/>
+      <c r="T44" s="28"/>
+      <c r="U44" s="28"/>
+      <c r="V44" s="29"/>
     </row>
     <row r="45" spans="1:22" ht="23.1" customHeight="1">
       <c r="A45" s="9"/>
@@ -2639,102 +2646,102 @@
       <c r="V45" s="9"/>
     </row>
     <row r="46" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="35"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="35"/>
-      <c r="M46" s="35"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="35"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="35"/>
-      <c r="V46" s="36"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="37"/>
+      <c r="M46" s="37"/>
+      <c r="N46" s="37"/>
+      <c r="O46" s="37"/>
+      <c r="P46" s="37"/>
+      <c r="Q46" s="37"/>
+      <c r="R46" s="37"/>
+      <c r="S46" s="37"/>
+      <c r="T46" s="37"/>
+      <c r="U46" s="37"/>
+      <c r="V46" s="38"/>
     </row>
     <row r="47" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A47" s="28"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="29"/>
-      <c r="T47" s="29"/>
-      <c r="U47" s="29"/>
-      <c r="V47" s="30"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="31"/>
+      <c r="S47" s="31"/>
+      <c r="T47" s="31"/>
+      <c r="U47" s="31"/>
+      <c r="V47" s="32"/>
     </row>
     <row r="48" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A48" s="28"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="30"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
+      <c r="M48" s="31"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="31"/>
+      <c r="S48" s="31"/>
+      <c r="T48" s="31"/>
+      <c r="U48" s="31"/>
+      <c r="V48" s="32"/>
     </row>
     <row r="49" spans="1:22" ht="23.1" customHeight="1">
-      <c r="A49" s="31"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="32"/>
-      <c r="L49" s="32"/>
-      <c r="M49" s="32"/>
-      <c r="N49" s="32"/>
-      <c r="O49" s="32"/>
-      <c r="P49" s="32"/>
-      <c r="Q49" s="32"/>
-      <c r="R49" s="32"/>
-      <c r="S49" s="32"/>
-      <c r="T49" s="32"/>
-      <c r="U49" s="32"/>
-      <c r="V49" s="33"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="34"/>
+      <c r="K49" s="34"/>
+      <c r="L49" s="34"/>
+      <c r="M49" s="34"/>
+      <c r="N49" s="34"/>
+      <c r="O49" s="34"/>
+      <c r="P49" s="34"/>
+      <c r="Q49" s="34"/>
+      <c r="R49" s="34"/>
+      <c r="S49" s="34"/>
+      <c r="T49" s="34"/>
+      <c r="U49" s="34"/>
+      <c r="V49" s="35"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
